--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -1744,7 +1744,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Flag is 1 when LOT N induction has BOTH (a) &gt;=1 valid mono-maintenance agent OR a valid dual combo, AND (b) an anchor agent. Mono: LENA, BORT, DARA, IXAZ, THAL. Dual: BORT+LENA, CARF+LENA, DARA+LENA. The anchor can itself be an approved agent; it does not need to be a non-maintenance agent.</t>
+          <t>Flag is 1 when LOT N induction has BOTH (a) &gt;=1 valid mono-maintenance agent OR a valid dual combo, AND (b) an anchor agent. Mono: LENA, BORT, DARA, IXAZ, THAL. Dual: BORT+LENA, CARF+LENA, DARA+LENA.</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Flag is 1 when LOTN_START_TYPE = SCT_ALLO. ALLO LOT contains no MM therapies. ALLO LOT spans a single day: start = end = ALLO_DT.</t>
+          <t>Flag is 1 when LOTN_START_TYPE = SCT_ALLO. ALLO LOT contains no MM therapies. Working rule (pending Julia confirmation): ALLO LOT spans a single day, start = end = ALLO_DT.</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>DARA + LENA is a valid dual maintenance regimen; the two agents anchor each other (anchor does not have to be non-maintenance).</t>
+          <t>DARA + LENA is a valid dual maintenance regimen; the two agents anchor each other.</t>
         </is>
       </c>
       <c r="D32" s="9" t="n"/>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>PRIMARY: earliest of (1) all-agent discontinuation (run-out date); (2) new qualifying MM agent (day before MAP_START_DT); (3) ALLO SCT (day before); (4) unplanned AUTO &gt;180d after prior AUTO (day before); (5) CAR-T (day before FIRST_CART_DT); (6) CART_INIT: when a CAR-T infusion occurs within 45 days of the first new agent that breaks LOT N, the LOT ends at that first new agent's day-before and reason = CART_INIT; (7) death (YMDOD); (8) study_end. Disenrollment is NOT a primary end event. SENSITIVITY: additionally cap at ENDDATE_CE when CENSOR_AT_DISENROLLMENT = TRUE.</t>
+          <t>PRIMARY: earliest of (1) all-agent discontinuation (run-out date); (2) new qualifying MM agent (day before MAP_START_DT); (3) ALLO SCT (day before); (4) unplanned AUTO &gt;180d after prior AUTO (day before); (5) CAR-T (day before FIRST_CART_DT); (6) CART_INIT: when CAR-T occurs within 45 days of the first new agent that breaks LOT N, the new agent is consolidated into CART_INIT and the LOT ends at FIRST_CART_DT - 1; (7) death (YMDOD); (8) study_end. Disenrollment is NOT a primary end event. SENSITIVITY: additionally cap at ENDDATE_CE when CENSOR_AT_DISENROLLMENT = TRUE.</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Draft: single day (start=end=ALLO_DT).</t>
+          <t>Working rule (used throughout draft, pending sign-off): single day, start = end = ALLO_DT.</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -2264,7 +2264,7 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>ALLO LOT spans a single day: start = end = ALLO_DT.</t>
+          <t>Working rule (pending confirmation): ALLO LOT spans a single day, so end = ALLO_DT.</t>
         </is>
       </c>
       <c r="D45" s="9" t="n"/>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>ALLO LOT span: single day (start = end = ALLO_DT). CAR-T LOT spans through last consolidation MAP_END_DT.</t>
+          <t>Working rule (pending confirmation): ALLO LOT spans a single day, start = end = ALLO_DT. CAR-T LOT spans through last consolidation MAP_END_DT.</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>ALLO LOT spans a single day: start = end = ALLO_DT.</t>
+          <t>Working rule (pending confirmation): ALLO LOT spans a single day, start = end = ALLO_DT.</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>LOT2: start = end = ALLO_DT (single-day ALLO LOT, no MM). Next agent starts LOT3.</t>
+          <t>LOT2: start = end = ALLO_DT, no MM (working rule: single-day ALLO LOT, pending confirmation). Next agent starts LOT3.</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Single-day ALLO LOT: start = end = ALLO_DT.</t>
+          <t>Working rule (pending confirmation): single-day ALLO LOT, start = end = ALLO_DT.</t>
         </is>
       </c>
     </row>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -3872,7 +3872,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Cap via ENDDATE_CE only when CENSOR_AT_DISENROLLMENT = TRUE. Q12.</t>
+          <t>Cap via ENDDATE_CE only when CENSOR_AT_DISENROLLMENT = TRUE.</t>
         </is>
       </c>
     </row>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -2597,7 +2597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2808,34 +2808,30 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>MEDICAL_DAY_SUPPLY</t>
+          <t>ALLO_ALWAYS_ENDS_LOT</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Assumed medical days supply</t>
+          <t>ALLO always ends current LOT</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Default for missing/anomalous DAY_SUPPLY (medical and pharmacy).</t>
+          <t>Any ALLO ends current LOT day before ALLO, and starts a new ALLO LOT.</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Use COALESCE; do NOT delete claims.</t>
-        </is>
-      </c>
+          <t>CL_SCT_CODELIST (ALLO)</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr"/>
       <c r="H6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
@@ -2846,30 +2842,34 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>ALLO_ALWAYS_ENDS_LOT</t>
+          <t>AUTO_TANDEM_WINDOW</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>ALLO always ends current LOT</t>
+          <t>Tandem AUTO window</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>60-180 days</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Any ALLO ends current LOT day before ALLO, and starts a new ALLO LOT.</t>
+          <t>Two AUTOs &gt;=60 and &lt;=180 days apart = planned tandem (same LOT). &gt;180 days = unplanned (new LOT).</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>CL_SCT_CODELIST (ALLO)</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr"/>
+          <t>CL_SCT_CODELIST (AUTO)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Use datediff without +1.</t>
+        </is>
+      </c>
       <c r="H7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -2880,32 +2880,32 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>AUTO_TANDEM_WINDOW</t>
+          <t>CART_CONSOLIDATION_DAYS</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Tandem AUTO window</t>
+          <t>CAR-T consolidation window</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>60-180 days</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Two AUTOs &gt;=60 and &lt;=180 days apart = planned tandem (same LOT). &gt;180 days = unplanned (new LOT).</t>
+          <t>Agents within 45 days of FIRST_CART_DT are consolidated into the CAR-T LOT (study-team decision).</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>CL_SCT_CODELIST (AUTO)</t>
+          <t>CL_SCT_CODELIST (CART)</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Use datediff without +1.</t>
+          <t>Do NOT advance to LOT_(N+1) for consolidated agents.</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
@@ -2918,32 +2918,32 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>CART_CONSOLIDATION_DAYS</t>
+          <t>LOTN_BASE_END_DT</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>CAR-T consolidation window</t>
+          <t>Final LOT N end date (PRIMARY)</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Agents within 45 days of FIRST_CART_DT are consolidated into the CAR-T LOT (study-team decision).</t>
+          <t>Earliest qualifying end event from LOTN_END_DT_TEMP. Also: CART_INIT applies when a CAR-T infusion occurs within 45 days of the first new agent that breaks LOT N.</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>CL_SCT_CODELIST (CART)</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Do NOT advance to LOT_(N+1) for consolidated agents.</t>
+          <t>Working rule (pending confirmation): ALLO LOT spans a single day, start = end = ALLO_DT. CAR-T LOT spans through last consolidation MAP_END_DT.</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr"/>
@@ -2956,22 +2956,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_DT</t>
+          <t>LOTN_BASE_END_REASON</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Final LOT N end date (PRIMARY)</t>
+          <t>Final LOT N end reason (PRIMARY)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>SCT_ALLO / SCT_CART / SCT_AUTO / CART_INIT / MED_ADD / DISCONTINUATION / DEATH / STUDY_END</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Earliest qualifying end event from LOTN_END_DT_TEMP. Also: CART_INIT applies when a CAR-T infusion occurs within 45 days of the first new agent that breaks LOT N.</t>
+          <t>Reason corresponding to LOTN_BASE_END_DT. DISENROLLMENT only in sensitivity (see *_CE_SENS).</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Working rule (pending confirmation): ALLO LOT spans a single day, start = end = ALLO_DT. CAR-T LOT spans through last consolidation MAP_END_DT.</t>
+          <t>DRAFT same-day priority (inherits LOT1 - confirm): SCT_ALLO &gt; SCT_CART &gt; SCT_AUTO &gt; CART_INIT &gt; MED_ADD &gt; DISCONTINUATION &gt; DEATH &gt; STUDY_END. CART_INIT logic inherits LOT1 (CAR-T within 45d of first add) - confirm applies to LOT2-5.</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
@@ -2994,32 +2994,32 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_REASON</t>
+          <t>LOTN_BASE_END_DT_CE_SENS</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Final LOT N end reason (PRIMARY)</t>
+          <t>LOT N end date (SENSITIVITY)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>SCT_ALLO / SCT_CART / SCT_AUTO / CART_INIT / MED_ADD / DISCONTINUATION / DEATH / STUDY_END</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Reason corresponding to LOTN_BASE_END_DT. DISENROLLMENT only in sensitivity (see *_CE_SENS).</t>
+          <t>Same as LOTN_BASE_END_DT, additionally capped at ELIGEND. Emitted when CENSOR_AT_DISENROLLMENT = TRUE.</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>T_MEMBER_CONT_ENROLLMENT</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>DRAFT same-day priority (inherits LOT1 - confirm): SCT_ALLO &gt; SCT_CART &gt; SCT_AUTO &gt; CART_INIT &gt; MED_ADD &gt; DISCONTINUATION &gt; DEATH &gt; STUDY_END. CART_INIT logic inherits LOT1 (CAR-T within 45d of first add) - confirm applies to LOT2-5.</t>
+          <t>Primary LOTN_BASE_END_DT untouched.</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr"/>
@@ -3032,32 +3032,32 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_DT_CE_SENS</t>
+          <t>LOTN_BASE_END_REASON_CE_SENS</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>LOT N end date (SENSITIVITY)</t>
+          <t>LOT N end reason (SENSITIVITY)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>(primary set) + DISENROLLMENT</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Same as LOTN_BASE_END_DT, additionally capped at ELIGEND. Emitted when CENSOR_AT_DISENROLLMENT = TRUE.</t>
+          <t>Same as primary, plus DISENROLLMENT when ELIGEND binds.</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>T_MEMBER_CONT_ENROLLMENT</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Primary LOTN_BASE_END_DT untouched.</t>
+          <t>REQUIRED: emit DISENROLLMENT (do NOT collapse to STUDY_END). Diverges from current LOT1 behaviour.</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr"/>
@@ -3070,22 +3070,22 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_REASON_CE_SENS</t>
+          <t>LOTN_BASE_LENGTH</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>LOT N end reason (SENSITIVITY)</t>
+          <t>LOT N duration (days)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>(primary set) + DISENROLLMENT</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Same as primary, plus DISENROLLMENT when ELIGEND binds.</t>
+          <t>If reason = DISCONTINUATION: LOTN_BASE_DISCON_DT - LOTN_START_DT + 1. Else: LOTN_BASE_END_DT - LOTN_START_DT + 1.</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -3095,140 +3095,112 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>REQUIRED: emit DISENROLLMENT (do NOT collapse to STUDY_END). Diverges from current LOT1 behaviour.</t>
+          <t>Confirm censored handling (LOT1 M1).</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>FU_PD</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>LOTN_BASE_LENGTH</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>LOT N duration (days)</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>If reason = DISCONTINUATION: LOTN_BASE_DISCON_DT - LOTN_START_DT + 1. Else: LOTN_BASE_END_DT - LOTN_START_DT + 1.</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Confirm censored handling (LOT1 M1).</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>FU_PD</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>PERMISSIBLE_SUBS_EFFECT</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Biosimilar substitution rule</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Do not advance LOT</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>Biosimilar swap within a reference product family does not end/advance the LOT. Regimen named by longest-duration drug.</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>permissible_subs</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>WORKED EXAMPLE D - End-reason priority with CART_INIT</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>LOT3 starts 2025-11-01 (KRd). Competing events: run-out 2026-04-15; POMA add 2026-03-20; CAR-T 2026-04-02 (within 45d of POMA); death 2026-05-20. Priority resolves to CART_INIT.</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="11" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="11" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Value for this patient</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>How it was derived</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="12" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>LOTN_BASE_END_DT</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>FIRST_CART_DT - 1.</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="9" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>Value for this patient</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>How it was derived</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="12" t="n"/>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>LOTN_BASE_END_REASON</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>CART_INIT</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>CART_INIT outranks MED_ADD; CAR-T within 45d of first add.</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_DT</t>
+          <t>LOTN_BASE_LENGTH</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>152</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>FIRST_CART_DT - 1.</t>
+          <t>2026-04-01 - 2025-11-01 + 1.</t>
         </is>
       </c>
       <c r="D21" s="9" t="n"/>
@@ -3240,17 +3212,17 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_REASON</t>
+          <t>LOT_(N+1)_START_DT</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>CART_INIT</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>CART_INIT outranks MED_ADD; CAR-T within 45d of first add.</t>
+          <t>LOT4_START_TYPE = CART.</t>
         </is>
       </c>
       <c r="D22" s="9" t="n"/>
@@ -3259,107 +3231,107 @@
       <c r="G22" s="9" t="n"/>
       <c r="H22" s="9" t="n"/>
     </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>LOTN_BASE_LENGTH</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-01 - 2025-11-01 + 1.</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>LOT_(N+1)_START_DT</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>LOT4_START_TYPE = CART.</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>WORKED EXAMPLE E - Discontinuation (run-out)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>LOT2 starts 2025-08-20 (DARA+LENA). Last LENA MAP_END_DT 2026-02-06; last DARA 2026-01-15. No new agent in 90d.</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-      <c r="H28" s="11" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="11" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Value for this patient</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>How it was derived</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>LOTN_BASE_DISCON_DT</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>max(MAP_END_DT) across LOT2 induction agents.</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="9" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>Value for this patient</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>How it was derived</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="12" t="n"/>
-      <c r="G29" s="12" t="n"/>
-      <c r="H29" s="12" t="n"/>
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>LOTN_BASE_END_DT</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Run-out date itself when reason = DISCONTINUATION.</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="9" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_DISCON_DT</t>
+          <t>LOTN_BASE_END_REASON</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>DISCONTINUATION</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>max(MAP_END_DT) across LOT2 induction agents.</t>
+          <t>Run-out reached; no agent within 90d gap.</t>
         </is>
       </c>
       <c r="D30" s="9" t="n"/>
@@ -3371,17 +3343,17 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_DT</t>
+          <t>LOTN_BASE_LENGTH</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>171</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Run-out date itself when reason = DISCONTINUATION.</t>
+          <t>2026-02-06 - 2025-08-20 + 1.</t>
         </is>
       </c>
       <c r="D31" s="9" t="n"/>
@@ -3390,107 +3362,103 @@
       <c r="G31" s="9" t="n"/>
       <c r="H31" s="9" t="n"/>
     </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>LOTN_BASE_END_REASON</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>DISCONTINUATION</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Run-out reached; no agent within 90d gap.</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9" t="n"/>
-      <c r="G32" s="9" t="n"/>
-      <c r="H32" s="9" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>LOTN_BASE_LENGTH</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>2026-02-06 - 2025-08-20 + 1.</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>WORKED EXAMPLE F - Disenrollment primary vs sensitivity</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>LOT4 starts 2026-01-05. ELIGEND 2026-04-30; no death; study_end 2026-12-31.</t>
         </is>
       </c>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="10" t="n"/>
-      <c r="H37" s="11" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+      <c r="H35" s="11" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>Value for this patient</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>How it was derived</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="12" t="n"/>
+      <c r="H36" s="12" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>LOTN_BASE_END_DT (PRIMARY)</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Disenrollment ignored; min(death, study_end) = study_end.</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>Value for this patient</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>How it was derived</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="12" t="n"/>
-      <c r="G38" s="12" t="n"/>
-      <c r="H38" s="12" t="n"/>
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>LOTN_BASE_END_REASON (PRIMARY)</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>STUDY_END</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="9" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_DT (PRIMARY)</t>
+          <t>LOTN_BASE_END_DT_CE_SENS</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Disenrollment ignored; min(death, study_end) = study_end.</t>
+          <t>ELIGEND binds.</t>
         </is>
       </c>
       <c r="D39" s="9" t="n"/>
@@ -3502,15 +3470,19 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_REASON (PRIMARY)</t>
+          <t>LOTN_BASE_END_REASON_CE_SENS</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>STUDY_END</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr"/>
+          <t>DISENROLLMENT</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Required: do NOT collapse to STUDY_END.</t>
+        </is>
+      </c>
       <c r="D40" s="9" t="n"/>
       <c r="E40" s="9" t="n"/>
       <c r="F40" s="9" t="n"/>
@@ -3520,17 +3492,17 @@
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_DT_CE_SENS</t>
+          <t>LOTN_BASE_LENGTH (PRIMARY)</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>ELIGEND binds.</t>
+          <t>2026-12-31 - 2026-01-05 + 1.</t>
         </is>
       </c>
       <c r="D41" s="9" t="n"/>
@@ -3542,17 +3514,17 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_REASON_CE_SENS</t>
+          <t>LOTN_BASE_LENGTH_CE_SENS</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>DISENROLLMENT</t>
+          <t>116</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Required: do NOT collapse to STUDY_END.</t>
+          <t>2026-04-30 - 2026-01-05 + 1.</t>
         </is>
       </c>
       <c r="D42" s="9" t="n"/>
@@ -3561,75 +3533,31 @@
       <c r="G42" s="9" t="n"/>
       <c r="H42" s="9" t="n"/>
     </row>
-    <row r="43">
-      <c r="A43" s="13" t="inlineStr">
-        <is>
-          <t>LOTN_BASE_LENGTH (PRIMARY)</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>2026-12-31 - 2026-01-05 + 1.</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="n"/>
-      <c r="E43" s="9" t="n"/>
-      <c r="F43" s="9" t="n"/>
-      <c r="G43" s="9" t="n"/>
-      <c r="H43" s="9" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="13" t="inlineStr">
-        <is>
-          <t>LOTN_BASE_LENGTH_CE_SENS</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-30 - 2026-01-05 + 1.</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="n"/>
-      <c r="E44" s="9" t="n"/>
-      <c r="F44" s="9" t="n"/>
-      <c r="G44" s="9" t="n"/>
-      <c r="H44" s="9" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="23">
     <mergeCell ref="C41:H41"/>
-    <mergeCell ref="C44:H44"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="C40:H40"/>
     <mergeCell ref="C31:H31"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="C43:H43"/>
     <mergeCell ref="C21:H21"/>
-    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="C39:H39"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="C19:H19"/>
     <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C18:H18"/>
     <mergeCell ref="C30:H30"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="A17:H17"/>
     <mergeCell ref="C42:H42"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="C20:H20"/>
     <mergeCell ref="C29:H29"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -4038,7 +4038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4083,12 +4083,12 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>90-day discontinuation gap inherited from LOT1?</t>
+          <t>90-day discontinuation gap - keep, or remove?</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>Draft: yes.</t>
+          <t>Per Julia 06-May: we are NOT using the 90d gap rule. Run-out = LOT end with reason DISCONTINUATION. Open scope question: does removal apply to LOT2-5 only, or to LOT1 as well (lot_program.R:757)? Removing from LOT1 will shift the LOT1 end-reason distribution (some STUDY_END / DEATH cases become DISCONTINUATION).</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -4434,17 +4434,17 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Same-day end-reason priority for LOT2-5 - inherits LOT1?</t>
+          <t>Same-day SCT/ALLO/CART/AUTO representation for LOT2-5.</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Draft: SCT_ALLO &gt; SCT_CART &gt; SCT_AUTO &gt; CART_INIT &gt; MED_ADD &gt; DISCONTINUATION &gt; DEATH &gt; STUDY_END (DISENROLLMENT in sensitivity). Confirm.</t>
+          <t>Per Julia 06-May: 'all events should be equally represented.' Current code uses scalar priority (SCT_ALLO &gt; CART &gt; SCT_AUTO &gt; MED) and records one LOT_START_TYPE. Action needed: run prevalence count of same-day collisions; then choose representation (scalar+priority / scalar+per-event flags / composite label / multi-row).</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Julia / Peter / Onkar</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -4475,6 +4475,33 @@
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Q16</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>AUTO trigger: 'always except induction/consolidation window'?</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Per Julia 06-May (sct/cart tab): 'Would update to also be Always, as long as it's outside of the induction window.' Today (lot2_5_base.R:259-260): AUTO triggers a new LOT only if there's a prior AUTO &gt;180d earlier; first-ever AUTOs are excluded. Proposed revised rule: 'AUTO starts a new LOT unless (i) inside the prior LOT's applicable window (30d MED/AUTO, 45d CART), or (ii) 60-180d after a prior AUTO (tandem).' Confirm: (a) rule wording; (b) scope - LOT2-5 only or LOT1 as well (LOT1 currently treats first AUTO as part of induction, lot_program.R:1300-1309).</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Julia / Peter</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -4439,17 +4439,17 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Per Julia 06-May: 'all events should be equally represented.' Current code uses scalar priority (SCT_ALLO &gt; CART &gt; SCT_AUTO &gt; MED) and records one LOT_START_TYPE. Action needed: run prevalence count of same-day collisions; then choose representation (scalar+priority / scalar+per-event flags / composite label / multi-row).</t>
+          <t>RESOLVED: keep scalar priority (SCT_ALLO &gt; CART &gt; SCT_AUTO &gt; MED) inherited from LOT1. LOTN_START_TYPE records the highest-priority event on the start date.</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Julia / Peter / Onkar</t>
+          <t>Julia / Peter</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -1304,7 +1304,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>Earliest of, after LOT_(N-1)_BASE_END_DT: (a) first non-steroid MM oncology agent; (b) first ALLO SCT; (c) first CAR-T infusion; (d) first UNPLANNED AUTO SCT (&gt;180d after a prior AUTO). Planned/single/tandem AUTO is a continuation, not a trigger. Permissible biosimilar substitutions do not trigger.</t>
+          <t>Earliest of, after LOT_(N-1)_BASE_END_DT: (a) first non-steroid MM oncology agent; (b) first ALLO SCT; (c) first CAR-T infusion; (d) first AUTO SCT, EXCEPT (i) when it falls inside LOT_(N-1)'s applicable window (30d for MED/AUTO-started LOTs, 1d for ALLO-started LOTs, 45d for CART-started LOTs) or (ii) when it is 60-180 days after the immediately prior AUTO (planned tandem - continuation, not a trigger). Permissible biosimilar substitutions do not trigger.</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>Source: T_MEDICAL (PROC_CD, BILL_PROC_CD, NDC), T_RX (NDC). Steroids excluded (MAP_MED_CLASS != 'STEROID').</t>
+          <t>Source: T_MEDICAL (PROC_CD, BILL_PROC_CD, NDC), T_RX (NDC). Steroids excluded (MAP_MED_CLASS != 'STEROID'). LOT2-5 only; LOT1 retains protocol convention that first AUTO is part of induction.</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr"/>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Flag is 1 when LOTN_START_TYPE = SCT_ALLO. ALLO LOT contains no MM therapies. Working rule (pending Julia confirmation): ALLO LOT spans a single day, start = end = ALLO_DT.</t>
+          <t>Flag is 1 when LOTN_START_TYPE = SCT_ALLO. ALLO LOT contains no MM therapies and spans a single day: start = end = ALLO_DT. ALLO is treated as a punctuation event between LOTs; the next MM agent starts the following LOT.</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Working rule (pending confirmation): ALLO LOT spans a single day, so end = ALLO_DT.</t>
+          <t>ALLO LOT spans a single day, so end = ALLO_DT.</t>
         </is>
       </c>
       <c r="D45" s="9" t="n"/>
@@ -2323,7 +2323,7 @@
     <row r="51" ht="60" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>Single AUTO 2025-03-01 in LOT1; second AUTO 2025-10-15 (228d later, unplanned). LOT1 ends 2025-10-14; LOT2 starts on AUTO.</t>
+          <t>VRd in LOT1 (60d induction). AUTO on 2025-10-15, no prior AUTO. LOT1 ends 2025-10-14 (AUTO is outside LOT1's 60d window). LOT2 starts on AUTO.</t>
         </is>
       </c>
       <c r="B51" s="10" t="n"/>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Unplanned AUTO date (&gt;180d after prior AUTO).</t>
+          <t>AUTO outside LOT1's applicable window and not a planned tandem.</t>
         </is>
       </c>
       <c r="D54" s="9" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Unplanned AUTO is a first-class LOT-start trigger. (Planned tandem 60-180d would NOT start a new LOT.)</t>
+          <t>AUTO is a first-class LOT-start trigger (LOT2-5). Planned tandem (60-180d after a prior AUTO) would NOT start a new LOT.</t>
         </is>
       </c>
       <c r="D55" s="9" t="n"/>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>PRIMARY: earliest of (1) all-agent discontinuation (run-out date); (2) new qualifying MM agent (day before MAP_START_DT); (3) ALLO SCT (day before); (4) unplanned AUTO &gt;180d after prior AUTO (day before); (5) CAR-T (day before FIRST_CART_DT); (6) CART_INIT: when CAR-T occurs within 45 days of the first new agent that breaks LOT N, the new agent is consolidated into CART_INIT and the LOT ends at FIRST_CART_DT - 1; (7) death (YMDOD); (8) study_end. Disenrollment is NOT a primary end event. SENSITIVITY: additionally cap at ENDDATE_CE when CENSOR_AT_DISENROLLMENT = TRUE.</t>
+          <t>PRIMARY: earliest of (1) all-agent discontinuation (run-out date); (2) new qualifying MM agent (day before MAP_START_DT); (3) ALLO SCT (day before); (4) AUTO that triggers a new LOT (day before), per the LOTN_START_DT trigger rule (any AUTO outside LOT N's applicable window and not 60-180d after a prior AUTO); (5) CAR-T (day before FIRST_CART_DT); (6) CART_INIT: when CAR-T occurs within 45 days of the first new agent that breaks LOT N, the new agent is consolidated into CART_INIT and the LOT ends at FIRST_CART_DT - 1; (7) death (YMDOD); (8) study_end. Disenrollment is NOT a primary end event. SENSITIVITY: additionally cap at ENDDATE_CE when CENSOR_AT_DISENROLLMENT = TRUE.</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Two AUTOs &gt;=60 and &lt;=180 days apart = planned tandem (same LOT). &gt;180 days = unplanned (new LOT).</t>
+          <t>Two AUTOs &gt;=60 and &lt;=180 days apart = planned tandem (continuation, no new LOT). Any other AUTO that falls outside LOT_(N-1)'s applicable window starts a new LOT.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Working rule (pending confirmation): ALLO LOT spans a single day, start = end = ALLO_DT. CAR-T LOT spans through last consolidation MAP_END_DT.</t>
+          <t>ALLO LOT spans a single day, start = end = ALLO_DT. CAR-T LOT spans through last consolidation MAP_END_DT.</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>Working rule (pending confirmation): ALLO LOT spans a single day, start = end = ALLO_DT.</t>
+          <t>ALLO LOT spans a single day: start = end = ALLO_DT.</t>
         </is>
       </c>
     </row>
@@ -3679,12 +3679,12 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Unplanned AUTO</t>
+          <t>AUTO SCT</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>&gt;180d after prior AUTO in LOT_(N-1).</t>
+          <t>Always, UNLESS (i) within LOT_(N-1)'s applicable window (30d MED/AUTO, 1d ALLO, 45d CART) or (ii) 60-180 days after a prior AUTO (planned tandem).</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Planned tandem (60-180d) does NOT start a new LOT.</t>
+          <t>First-ever AUTOs CAN trigger a new LOT (LOT2-5 only). LOT1 keeps protocol convention that the first AUTO is part of induction.</t>
         </is>
       </c>
     </row>
@@ -3860,17 +3860,17 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>S2. LOT1-&gt;LOT2 by unplanned AUTO</t>
+          <t>S2. LOT1-&gt;LOT2 by AUTO outside window</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Single AUTO d100; second AUTO d320 (220d later).</t>
+          <t>AUTO d320, outside LOT1's induction window and not 60-180d after a prior AUTO.</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>LOT1 ends d319. LOT2_START_DT=d320, TYPE=SCT_AUTO.</t>
+          <t>LOT1 ends d319. LOT2_START_DT=d320, TYPE=SCT_AUTO. (Planned tandem 60-180d after a prior AUTO would NOT trigger.)</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>LOT2: start = end = ALLO_DT, no MM (working rule: single-day ALLO LOT, pending confirmation). Next agent starts LOT3.</t>
+          <t>LOT2: start = end = ALLO_DT, single-day ALLO LOT, no MM. Next agent starts LOT3.</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Working rule (pending confirmation): single-day ALLO LOT, start = end = ALLO_DT.</t>
+          <t>Single-day ALLO LOT: start = end = ALLO_DT.</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Working rule (used throughout draft, pending sign-off): single day, start = end = ALLO_DT.</t>
+          <t>RESOLVED: single day, start = end = ALLO_DT. ALLO is a punctuation event between LOTs; the next MM agent starts the following LOT.</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Per Julia 06-May (sct/cart tab): 'Would update to also be Always, as long as it's outside of the induction window.' Today (lot2_5_base.R:259-260): AUTO triggers a new LOT only if there's a prior AUTO &gt;180d earlier; first-ever AUTOs are excluded. Proposed revised rule: 'AUTO starts a new LOT unless (i) inside the prior LOT's applicable window (30d MED/AUTO, 45d CART), or (ii) 60-180d after a prior AUTO (tandem).' Confirm: (a) rule wording; (b) scope - LOT2-5 only or LOT1 as well (LOT1 currently treats first AUTO as part of induction, lot_program.R:1300-1309).</t>
+          <t>RESOLVED: AUTO starts a new LOT (in LOT2-5) unless (i) it falls inside LOT_(N-1)'s applicable window (30d for MED/AUTO-started LOTs, 1d for ALLO-started LOTs, 45d for CART-started LOTs) or (ii) it is 60-180 days after the immediately prior AUTO (planned tandem). Scope: LOT2-5 only. LOT1 retains the protocol convention that the first AUTO is part of induction (lot_program.R:1300-1309 unchanged). Code change required in lot2_5_base.R::auto_cand (Bucket C).</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -2703,7 +2703,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>LOT N run-out date</t>
+          <t>LOT N run-out date (last med date)</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>max(MAP_END_DT) across LOT N induction agents. Used as LOT end when reason = DISCONTINUATION.</t>
+          <t>max(MAP_END_DT) across LOT N induction agents - i.e., the last day of supply for any drug in the regimen. Populated whenever a runout exists, INCLUDING when a higher-priority reason (DEATH, SCT, etc.) wins the LOT end. Used as LOTN_BASE_END_DT only when LOTN_BASE_END_REASON = DISCONTINUATION.</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>T_MEDICAL: FST_DT + medical_day_supply - 1. T_RX: FILL_DT + DAYS_SUP - 1. Missing DAY_SUPPLY -&gt; 28d default (do not delete claims).</t>
+          <t>T_MEDICAL: FST_DT + medical_day_supply - 1. T_RX: FILL_DT + DAYS_SUP - 1. Missing DAY_SUPPLY -&gt; 28d default (do not delete claims). No LOT-level 90d observation buffer (removed per Julia 06-May).</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr"/>
@@ -2779,17 +2779,17 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Discontinuation gap (days)</t>
+          <t>LOT-level discontinuation buffer (days)</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Inherits LOT1.</t>
+          <t>REMOVED per Julia 06-May ('we are not using the 90d gap rule'). LOTN_BASE_DISCON_DT = last med date (max MAP_END_DT) whenever a runout exists; no observation-time buffer. Per-drug discontinuation detection still uses MAP-level map_discon_gap_days (unchanged).</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -2797,7 +2797,11 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Applies to both LOT1 and LOT2-5.</t>
+        </is>
+      </c>
       <c r="H5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
@@ -2966,7 +2970,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>SCT_ALLO / SCT_CART / SCT_AUTO / CART_INIT / MED_ADD / DISCONTINUATION / DEATH / STUDY_END</t>
+          <t>SCT_ALLO / SCT_CART / SCT_AUTO / CART_INIT / MED_ADD / DEATH / DISCONTINUATION / STUDY_END</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -2981,7 +2985,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>DRAFT same-day priority (inherits LOT1 - confirm): SCT_ALLO &gt; SCT_CART &gt; SCT_AUTO &gt; CART_INIT &gt; MED_ADD &gt; DISCONTINUATION &gt; DEATH &gt; STUDY_END. CART_INIT logic inherits LOT1 (CAR-T within 45d of first add) - confirm applies to LOT2-5.</t>
+          <t>Same-day / overlapping-event priority (revised per Julia 06-May to keep DEATH above DISCONTINUATION): SCT_ALLO &gt; SCT_CART &gt; SCT_AUTO &gt; CART_INIT &gt; MED_ADD &gt; DEATH &gt; DISCONTINUATION &gt; STUDY_END. DEATH moved above DISCONTINUATION so patients who run out and then die within the LOT keep REASON = DEATH (the runout date is still recorded in LOTN_BASE_DISCON_DT).</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
@@ -3241,7 +3245,7 @@
     <row r="26" ht="60" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>LOT2 starts 2025-08-20 (DARA+LENA). Last LENA MAP_END_DT 2026-02-06; last DARA 2026-01-15. No new agent in 90d.</t>
+          <t>LOT2 starts 2025-08-20 (DARA+LENA). Last LENA MAP_END_DT 2026-02-06; last DARA 2026-01-15. No new agent, no death, study continues.</t>
         </is>
       </c>
       <c r="B26" s="10" t="n"/>
@@ -3287,7 +3291,7 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>max(MAP_END_DT) across LOT2 induction agents.</t>
+          <t>max(MAP_END_DT) across LOT2 induction agents (last med date).</t>
         </is>
       </c>
       <c r="D28" s="9" t="n"/>
@@ -3309,7 +3313,7 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Run-out date itself when reason = DISCONTINUATION.</t>
+          <t>Runout = LOT end (no LOT-level 90d buffer).</t>
         </is>
       </c>
       <c r="D29" s="9" t="n"/>
@@ -3331,7 +3335,7 @@
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Run-out reached; no agent within 90d gap.</t>
+          <t>Runout reached; no death or higher-priority event.</t>
         </is>
       </c>
       <c r="D30" s="9" t="n"/>
@@ -4088,7 +4092,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>Per Julia 06-May: we are NOT using the 90d gap rule. Run-out = LOT end with reason DISCONTINUATION. Open scope question: does removal apply to LOT2-5 only, or to LOT1 as well (lot_program.R:757)? Removing from LOT1 will shift the LOT1 end-reason distribution (some STUDY_END / DEATH cases become DISCONTINUATION).</t>
+          <t>RESOLVED. Reply to Julia (06-May comments 2c + 4c): Removing the LOT-level 90d confirmation gap from both LOT1 and LOT2-5 per your request. LOTN_BASE_DISCON_DT will always equal the last med date (max MAP_END_DT across induction agents) whenever a runout exists - no observation-time buffer. To preserve the death signal you'd otherwise lose, end-reason priority is flipped so DEATH &gt; DISCONTINUATION &gt; STUDY_END (was DISCONTINUATION &gt; DEATH &gt; STUDY_END). Effect: (1) patients who run out and die get REASON = DEATH at death date with LOT length to death (no change); (2) patients who run out and reach study end get REASON = DISCONTINUATION at runout (matches what you expected on the dashboard); (3) the runout date is still recorded in LOTN_BASE_DISCON_DT for downstream use even when REASON = DEATH. MAP-level discontinuation gap (map_discon_gap_days, per-drug) is UNCHANGED - still drives per-drug stop detection.</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -4098,7 +4102,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -5353,7 +5357,7 @@
     <row r="12" ht="50" customHeight="1">
       <c r="A12" s="43" t="inlineStr">
         <is>
-          <t>END-REASON same-day priority (separate from LOT-start tie-break in Step 3a; DRAFT, inherits LOT1 - confirm): SCT_ALLO &gt; SCT_CART &gt; SCT_AUTO &gt; CART_INIT &gt; MED_ADD &gt; DISCONTINUATION &gt; DEATH &gt; STUDY_END. SENSITIVITY adds DISENROLLMENT before STUDY_END. See LOTN_BASE_END_REASON in tab 4.</t>
+          <t>END-REASON priority (separate from LOT-start tie-break in Step 3a; revised per Julia 06-May): SCT_ALLO &gt; SCT_CART &gt; SCT_AUTO &gt; CART_INIT &gt; MED_ADD &gt; DEATH &gt; DISCONTINUATION &gt; STUDY_END. DEATH outranks DISCONTINUATION so patients who run out then die keep REASON = DEATH. SENSITIVITY adds DISENROLLMENT before STUDY_END. See LOTN_BASE_END_REASON in tab 4.</t>
         </is>
       </c>
     </row>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -1352,7 +1352,7 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Same-day tie-break (DRAFT, inherits LOT1 - confirm): SCT_ALLO &gt; CART &gt; SCT_AUTO &gt; MED.</t>
+          <t>Same-day tie-break (Q14 resolved, inherits LOT1): SCT_ALLO &gt; CART &gt; SCT_AUTO &gt; MED.</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr"/>
@@ -2316,14 +2316,14 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>WORKED EXAMPLE C - LOT2 starts on an unplanned autologous SCT</t>
+          <t>WORKED EXAMPLE C - LOT3 starts on an AUTO (first-ever; LOT2 ended outside its induction window)</t>
         </is>
       </c>
     </row>
     <row r="51" ht="60" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>VRd in LOT1 (60d induction). AUTO on 2025-10-15, no prior AUTO. LOT1 ends 2025-10-14 (AUTO is outside LOT1's 60d window). LOT2 starts on AUTO.</t>
+          <t>LOT1 ends 2025-04-30 via DISCONTINUATION (VRd run-out, no SCT during LOT1). LOT2 starts 2025-08-20 via MED_ADD (DARA + LENA, 30d induction window). First-ever AUTO occurs 2025-12-10, well outside LOT2's 30d induction window (2025-08-20 to 2025-09-18) and not 60-180d after any prior AUTO. Per Q16 (LOT2-5 only), this first-ever AUTO triggers LOT3 starting on the AUTO date. (LOT1 itself is unchanged - first AUTO in LOT1 would still be protocol-mandated induction.)</t>
         </is>
       </c>
       <c r="B51" s="10" t="n"/>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr"/>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>AUTO outside LOT1's applicable window and not a planned tandem.</t>
+          <t>AUTO outside LOT2's 30d window (LOT2 was MED-started) and not a planned tandem.</t>
         </is>
       </c>
       <c r="D54" s="9" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>AUTO is a first-class LOT-start trigger (LOT2-5). Planned tandem (60-180d after a prior AUTO) would NOT start a new LOT.</t>
+          <t>AUTO is a first-class LOT-start trigger for LOT2-5 (Q16). Planned tandem (60-180d after a prior AUTO) would NOT start a new LOT.</t>
         </is>
       </c>
       <c r="D55" s="9" t="n"/>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>No MM therapies recorded in the [2025-10-15, 2025-11-13] post-AUTO induction window.</t>
+          <t>No MM therapies recorded in the [2025-12-10, 2026-01-08] post-AUTO induction window.</t>
         </is>
       </c>
       <c r="D56" s="9" t="n"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>LOT2 captures any post-AUTO agents within [2025-10-15, 2025-11-13].</t>
+          <t>LOT3 captures any post-AUTO agents within [2025-12-10, 2026-01-08].</t>
         </is>
       </c>
       <c r="D58" s="9" t="n"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>AUTO occurred during LOT2.</t>
+          <t>AUTO occurred during LOT3.</t>
         </is>
       </c>
       <c r="D59" s="9" t="n"/>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Single AUTO during LOT2 (no second AUTO within tandem window).</t>
+          <t>Single AUTO during LOT3 (no second AUTO within tandem window).</t>
         </is>
       </c>
       <c r="D60" s="9" t="n"/>
@@ -3864,17 +3864,17 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>S2. LOT1-&gt;LOT2 by AUTO outside window</t>
+          <t>S2. LOT2-&gt;LOT3 by AUTO outside window</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>AUTO d320, outside LOT1's induction window and not 60-180d after a prior AUTO.</t>
+          <t>LOT2 is MED-started (30d window). AUTO occurs d320 relative to LOT2 start, outside LOT2's window and not 60-180d after any prior AUTO.</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>LOT1 ends d319. LOT2_START_DT=d320, TYPE=SCT_AUTO. (Planned tandem 60-180d after a prior AUTO would NOT trigger.)</t>
+          <t>LOT2 ends d319. LOT3_START_DT = d320, TYPE = SCT_AUTO. Q16 applies to LOT2-5 only; LOT1's first AUTO remains part of induction.</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>RESOLVED: AUTO starts a new LOT (in LOT2-5) unless (i) it falls inside LOT_(N-1)'s applicable window (30d for MED/AUTO-started LOTs, 1d for ALLO-started LOTs, 45d for CART-started LOTs) or (ii) it is 60-180 days after the immediately prior AUTO (planned tandem). Scope: LOT2-5 only. LOT1 retains the protocol convention that the first AUTO is part of induction (lot_program.R:1300-1309 unchanged). Code change required in lot2_5_base.R::auto_cand (Bucket C).</t>
+          <t>RESOLVED + IMPLEMENTED: AUTO starts a new LOT (in LOT2-5) unless (i) it falls inside LOT_(N-1)'s applicable window (30d for MED/AUTO-started LOTs, 1d for ALLO-started LOTs, 45d for CART-started LOTs) or (ii) it is 60-180 days after the immediately prior AUTO (planned tandem). Scope: LOT2-5 only. LOT1 retains the protocol convention that the first AUTO is part of induction (lot_program.R:1300-1309 unchanged). Code implemented in lot2_5_base.R: auto_cand CTE and lot_n_sct ENDING_AUTO_DT now apply the window-by-type rule; prev_end CTE pulls PREV_START_DT and PREV_START_TYPE from lot_long for the window lookup.</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -4776,62 +4776,58 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>S2: LOT1 -&gt; LOT2 by unplanned AUTO</t>
+          <t>S2: LOT2 -&gt; LOT3 by AUTO outside window (Q16, LOT2-5 only)</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>Single AUTO d100; second AUTO d320 (&gt;180d) is unplanned -&gt; LOT2 starts d320</t>
+          <t>LOT1 ends d199 by MED_ADD. LOT2 (MED-started, 30d window d200-d229). First-ever AUTO at d320 - outside LOT2's window and not a tandem -&gt; LOT3 starts d320.</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr"/>
-      <c r="D6" s="32" t="inlineStr"/>
-      <c r="E6" s="32" t="inlineStr"/>
-      <c r="F6" s="32" t="inlineStr"/>
-      <c r="G6" s="32" t="inlineStr"/>
-      <c r="H6" s="32" t="inlineStr"/>
+      <c r="D6" s="31" t="inlineStr"/>
+      <c r="E6" s="31" t="inlineStr"/>
+      <c r="F6" s="31" t="inlineStr"/>
+      <c r="G6" s="31" t="inlineStr"/>
+      <c r="H6" s="31" t="inlineStr"/>
       <c r="I6" s="32" t="inlineStr"/>
       <c r="J6" s="32" t="inlineStr"/>
-      <c r="K6" s="36" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="K6" s="32" t="inlineStr"/>
       <c r="L6" s="32" t="inlineStr"/>
       <c r="M6" s="32" t="inlineStr"/>
       <c r="N6" s="32" t="inlineStr"/>
       <c r="O6" s="32" t="inlineStr"/>
       <c r="P6" s="32" t="inlineStr"/>
       <c r="Q6" s="32" t="inlineStr"/>
-      <c r="R6" s="32" t="inlineStr"/>
-      <c r="S6" s="32" t="inlineStr"/>
-      <c r="T6" s="32" t="inlineStr"/>
-      <c r="U6" s="32" t="inlineStr"/>
-      <c r="V6" s="32" t="inlineStr"/>
-      <c r="W6" s="32" t="inlineStr"/>
-      <c r="X6" s="32" t="inlineStr"/>
-      <c r="Y6" s="32" t="inlineStr"/>
+      <c r="R6" s="34" t="inlineStr"/>
+      <c r="S6" s="34" t="inlineStr"/>
+      <c r="T6" s="34" t="inlineStr"/>
+      <c r="U6" s="35" t="inlineStr"/>
+      <c r="V6" s="35" t="inlineStr"/>
+      <c r="W6" s="35" t="inlineStr"/>
+      <c r="X6" s="35" t="inlineStr"/>
+      <c r="Y6" s="35" t="inlineStr"/>
       <c r="Z6" s="37" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AA6" s="34" t="inlineStr"/>
-      <c r="AB6" s="34" t="inlineStr"/>
-      <c r="AC6" s="35" t="inlineStr"/>
-      <c r="AD6" s="35" t="inlineStr"/>
-      <c r="AE6" s="35" t="inlineStr"/>
-      <c r="AF6" s="35" t="inlineStr"/>
-      <c r="AG6" s="35" t="inlineStr"/>
-      <c r="AH6" s="35" t="inlineStr"/>
-      <c r="AI6" s="35" t="inlineStr"/>
-      <c r="AJ6" s="35" t="inlineStr"/>
-      <c r="AK6" s="35" t="inlineStr"/>
-      <c r="AL6" s="35" t="inlineStr"/>
-      <c r="AM6" s="35" t="inlineStr"/>
-      <c r="AN6" s="35" t="inlineStr"/>
-      <c r="AO6" s="35" t="inlineStr"/>
-      <c r="AP6" s="35" t="inlineStr"/>
+      <c r="AA6" s="39" t="inlineStr"/>
+      <c r="AB6" s="39" t="inlineStr"/>
+      <c r="AC6" s="40" t="inlineStr"/>
+      <c r="AD6" s="40" t="inlineStr"/>
+      <c r="AE6" s="40" t="inlineStr"/>
+      <c r="AF6" s="40" t="inlineStr"/>
+      <c r="AG6" s="40" t="inlineStr"/>
+      <c r="AH6" s="40" t="inlineStr"/>
+      <c r="AI6" s="40" t="inlineStr"/>
+      <c r="AJ6" s="40" t="inlineStr"/>
+      <c r="AK6" s="40" t="inlineStr"/>
+      <c r="AL6" s="40" t="inlineStr"/>
+      <c r="AM6" s="40" t="inlineStr"/>
+      <c r="AN6" s="40" t="inlineStr"/>
+      <c r="AO6" s="40" t="inlineStr"/>
+      <c r="AP6" s="40" t="inlineStr"/>
       <c r="AQ6" s="30" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -5209,7 +5205,7 @@
   d_MED   = first non-steroid MM agent MAP_START_DT (excl. permissible biosimilar subs)
   d_ALLO  = first ALLO SCT date
   d_CART  = first CAR-T infusion date (FIRST_CART_DT)
-  d_AUTO  = first UNPLANNED AUTO date (&gt;180d after the most recent prior AUTO in the patient's history; if no prior AUTO, AUTO is NOT a candidate).</t>
+  d_AUTO  = first AUTO date (Q16, 06-May): triggers LOT_(N+1) unless (i) it falls inside LOT_N's applicable window from LOT_N_START_DT (30d for MED/AUTO-started LOTs, 1d for ALLO-started, 45d for CART-started) or (ii) it is 60-180 days after the immediately prior AUTO (planned tandem). First-ever AUTOs CAN trigger a new LOT (LOT2-5 only; LOT1 retains the protocol convention that the first AUTO is part of induction).</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -5219,7 +5215,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Planned/single/tandem AUTO (60-180d intervals) is a CONTINUATION and is NOT a candidate.</t>
+          <t>Planned tandem (60-180d after a prior AUTO) is a CONTINUATION and is NOT a candidate.</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5277,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Same-day tie-break (DRAFT, inherits LOT1 - confirm).</t>
+          <t>Same-day tie-break (Q14 resolved, inherits LOT1).</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -4092,7 +4092,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>RESOLVED. Reply to Julia (06-May comments 2c + 4c): Removing the LOT-level 90d confirmation gap from both LOT1 and LOT2-5 per your request. LOTN_BASE_DISCON_DT will always equal the last med date (max MAP_END_DT across induction agents) whenever a runout exists - no observation-time buffer. To preserve the death signal you'd otherwise lose, end-reason priority is flipped so DEATH &gt; DISCONTINUATION &gt; STUDY_END (was DISCONTINUATION &gt; DEATH &gt; STUDY_END). Effect: (1) patients who run out and die get REASON = DEATH at death date with LOT length to death (no change); (2) patients who run out and reach study end get REASON = DISCONTINUATION at runout (matches what you expected on the dashboard); (3) the runout date is still recorded in LOTN_BASE_DISCON_DT for downstream use even when REASON = DEATH. MAP-level discontinuation gap (map_discon_gap_days, per-drug) is UNCHANGED - still drives per-drug stop detection.</t>
+          <t>RESOLVED + IMPLEMENTED. Reply to Julia (06-May comments 2c + 4c): Removing the LOT-level 90d confirmation gap from both LOT1 and LOT2-5 per your request. LOTN_BASE_DISCON_DT will always equal the last med date (max MAP_END_DT across induction agents) whenever a runout exists - no observation-time buffer. To preserve the death signal, end-reason priority is flipped so DEATH &gt; DISCONTINUATION &gt; STUDY_END (was DISCONTINUATION &gt; DEATH &gt; STUDY_END). Edge-case refinement (Q1.1): DEATH only preempts DISCONTINUATION when no LOT-(N+1)-qualifying trigger exists in (DISCON_DT, OBS_END_DT]. If the patient ran out, started new therapy (or had an SCT), and then died, the runout is the true LOT N end (REASON = DISCONTINUATION) and the new event triggers LOT N+1 in the next iteration - prevents post-runout therapy from being silently swallowed by death. Effect: (1) runs out, dies, no post-runout therapy =&gt; REASON = DEATH at death date; (2) runs out, starts new therapy, then dies =&gt; REASON = DISCONTINUATION at runout; new therapy starts LOT N+1; (3) runs out, reaches study end =&gt; REASON = DISCONTINUATION at runout (matches dashboard expectation); (4) runout date is still recorded in LOTN_BASE_DISCON_DT even when REASON = DEATH. MAP-level discontinuation gap (map_discon_gap_days, per-drug) is UNCHANGED.</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -5118,7 +5118,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Each cell = ~14 days. Markers: M=Med add, A=AUTO SCT, X=ALLO SCT, C=CAR-T, +=Death. Yellow top edge = induction window overlay. Single-cell-only LOT = singleton ALLO LOT (Q2 draft assumption).</t>
+          <t>Each cell = ~14 days. Markers: M=Med add, A=AUTO SCT, X=ALLO SCT, C=CAR-T, +=Death. Yellow top edge = induction window overlay. Single-cell-only LOT = singleton ALLO LOT (Q2 resolved: ALLO LOT spans a single day).</t>
         </is>
       </c>
     </row>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -3772,7 +3772,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Disenrollment is NOT a primary end event.</t>
+          <t>Distinct from DISCONTINUATION. Per Q1 (06-May): runout cases now correctly show DISCONTINUATION on the dashboard - DEATH / STUDY_END no longer absorb runouts that previously hid behind the 90d buffer. Per Q1.1: if a patient runs out, starts new therapy, then dies, the runout is the LOT N end (REASON = DISCONTINUATION) and the new event triggers LOT N+1 - DEATH does not silently swallow post-runout therapy. Disenrollment is NOT a primary end event.</t>
         </is>
       </c>
     </row>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -3720,7 +3720,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>After LOT_(N-1) ended by DISCONTINUATION or MED_ADD with no SCT/CAR-T.</t>
+          <t>Always, when MAP_START_DT is strictly after LOT_(N-1)_BASE_END_DT (i.e., outside the prior LOT's span / induction window).</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Steroids and biosimilar subs do not start a LOT.</t>
+          <t>Steroids and biosimilar subs of LOT_(N-1) drugs do not start a LOT. Code: lot2_5_base.R::med_cand uses MAP_START_DT &gt; PREV_END_DT - no gating on the prior LOT's end reason.</t>
         </is>
       </c>
     </row>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -1304,7 +1304,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>Earliest of, after LOT_(N-1)_BASE_END_DT: (a) first non-steroid MM oncology agent; (b) first ALLO SCT; (c) first CAR-T infusion; (d) first AUTO SCT, EXCEPT (i) when it falls inside LOT_(N-1)'s applicable window (30d for MED/AUTO-started LOTs, 1d for ALLO-started LOTs, 45d for CART-started LOTs) or (ii) when it is 60-180 days after the immediately prior AUTO (planned tandem - continuation, not a trigger). Permissible biosimilar substitutions do not trigger.</t>
+          <t>Earliest of, after LOT_(N-1)_BASE_END_DT: (a) first non-steroid MM oncology agent; (b) first ALLO SCT; (c) first CAR-T infusion; (d) first AUTO SCT, EXCEPT (i) when it falls inside LOT_(N-1)'s applicable window (30d for MED/AUTO-started LOTs, 1d for ALLO-started LOTs, 45d for CART-started LOTs) or (ii) when it is on/before sct_tandem_days (180d) after the immediately prior AUTO (planned tandem - continuation, not a trigger). Permissible biosimilar substitutions do not trigger.</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -2323,7 +2323,7 @@
     <row r="51" ht="60" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>LOT1 ends 2025-04-30 via DISCONTINUATION (VRd run-out, no SCT during LOT1). LOT2 starts 2025-08-20 via MED_ADD (DARA + LENA, 30d induction window). First-ever AUTO occurs 2025-12-10, well outside LOT2's 30d induction window (2025-08-20 to 2025-09-18) and not 60-180d after any prior AUTO. Per Q16 (LOT2-5 only), this first-ever AUTO triggers LOT3 starting on the AUTO date. (LOT1 itself is unchanged - first AUTO in LOT1 would still be protocol-mandated induction.)</t>
+          <t>LOT1 ends 2025-04-30 via DISCONTINUATION (VRd run-out, no SCT during LOT1). LOT2 starts 2025-08-20 via MED_ADD (DARA + LENA, 30d induction window). First-ever AUTO occurs 2025-12-10, well outside LOT2's 30d induction window (2025-08-20 to 2025-09-18) and not within sct_tandem_days (&lt;=180d) of any prior AUTO. Per Q16 (LOT2-5 only), this first-ever AUTO triggers LOT3 starting on the AUTO date. (LOT1 itself is unchanged - first AUTO in LOT1 would still be protocol-mandated induction.)</t>
         </is>
       </c>
       <c r="B51" s="10" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>AUTO is a first-class LOT-start trigger for LOT2-5 (Q16). Planned tandem (60-180d after a prior AUTO) would NOT start a new LOT.</t>
+          <t>AUTO is a first-class LOT-start trigger for LOT2-5 (Q16). Planned tandem (within sct_tandem_days = 180d of a prior AUTO) would NOT start a new LOT.</t>
         </is>
       </c>
       <c r="D55" s="9" t="n"/>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>PRIMARY: earliest of (1) all-agent discontinuation (run-out date); (2) new qualifying MM agent (day before MAP_START_DT); (3) ALLO SCT (day before); (4) AUTO that triggers a new LOT (day before), per the LOTN_START_DT trigger rule (any AUTO outside LOT N's applicable window and not 60-180d after a prior AUTO); (5) CAR-T (day before FIRST_CART_DT); (6) CART_INIT: when CAR-T occurs within 45 days of the first new agent that breaks LOT N, the new agent is consolidated into CART_INIT and the LOT ends at FIRST_CART_DT - 1; (7) death (YMDOD); (8) study_end. Disenrollment is NOT a primary end event. SENSITIVITY: additionally cap at ENDDATE_CE when CENSOR_AT_DISENROLLMENT = TRUE.</t>
+          <t>PRIMARY: earliest of (1) all-agent discontinuation (run-out date); (2) new qualifying MM agent (day before MAP_START_DT); (3) ALLO SCT (day before); (4) AUTO that triggers a new LOT (day before), per the LOTN_START_DT trigger rule (any AUTO outside LOT N's applicable window and not within sct_tandem_days (&lt;=180d) of a prior AUTO); (5) CAR-T (day before FIRST_CART_DT); (6) CART_INIT: when CAR-T occurs within 45 days of the first new agent that breaks LOT N, the new agent is consolidated into CART_INIT and the LOT ends at FIRST_CART_DT - 1; (7) death (YMDOD); (8) study_end. Disenrollment is NOT a primary end event. SENSITIVITY: additionally cap at ENDDATE_CE when CENSOR_AT_DISENROLLMENT = TRUE.</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>60-180 days</t>
+          <t>&lt;= 180 days</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Two AUTOs &gt;=60 and &lt;=180 days apart = planned tandem (continuation, no new LOT). Any other AUTO that falls outside LOT_(N-1)'s applicable window starts a new LOT.</t>
+          <t>Two AUTOs &lt;= sct_tandem_days (180 days) apart = planned tandem (continuation, no new LOT). Any other AUTO that falls outside LOT_(N-1)'s applicable window starts a new LOT.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Use datediff without +1.</t>
+          <t>Per Julia 13-May: implementation uses ONLY the upper bound. The MM protocol convention is 60-180 days, but the &lt; 60 d case is too rare and ambiguous (usually re-conditioning / salvage rather than a planned tandem) to gate on. Matches LOT1's existing behaviour. Use datediff without +1.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr"/>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Always, UNLESS (i) within LOT_(N-1)'s applicable window (30d MED/AUTO, 1d ALLO, 45d CART) or (ii) 60-180 days after a prior AUTO (planned tandem).</t>
+          <t>Always, UNLESS (i) within LOT_(N-1)'s applicable window (30d MED/AUTO, 1d ALLO, 45d CART) or (ii) within sct_tandem_days (&lt;=180d) of a prior AUTO (planned tandem).</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>LOT2 is MED-started (30d window). AUTO occurs d320 relative to LOT2 start, outside LOT2's window and not 60-180d after any prior AUTO.</t>
+          <t>LOT2 is MED-started (30d window). AUTO occurs d320 relative to LOT2 start, outside LOT2's window and not within sct_tandem_days (&lt;=180d) of any prior AUTO.</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -4303,22 +4303,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Confirm tandem off-by-one fix (LOT1 H2).</t>
+          <t>Tandem AUTO window: just &lt;=180 days, or &gt;=60 AND &lt;=180 (protocol)?</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Required: drop +1 in datediff; window &gt;=60 AND &lt;=180.</t>
+          <t>RESOLVED per Julia 13-May: keep implementation at &lt;= sct_tandem_days (180) only. Ignore the &lt; 60 day case - rare and ambiguous (usually re-conditioning / salvage, not a planned tandem). The MM protocol describes tandem as 60-180 days; this is noted in the spec but not enforced in code. Matches existing LOT1 behaviour, keeping LOT1 and LOT2-5 consistent. datediff is used without +1.</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Onkar</t>
+          <t>Julia / Peter</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>RESOLVED + IMPLEMENTED: AUTO starts a new LOT (in LOT2-5) unless (i) it falls inside LOT_(N-1)'s applicable window (30d for MED/AUTO-started LOTs, 1d for ALLO-started LOTs, 45d for CART-started LOTs) or (ii) it is 60-180 days after the immediately prior AUTO (planned tandem). Scope: LOT2-5 only. LOT1 retains the protocol convention that the first AUTO is part of induction (lot_program.R:1300-1309 unchanged). Code implemented in lot2_5_base.R: auto_cand CTE and lot_n_sct ENDING_AUTO_DT now apply the window-by-type rule; prev_end CTE pulls PREV_START_DT and PREV_START_TYPE from lot_long for the window lookup.</t>
+          <t>RESOLVED + IMPLEMENTED: AUTO starts a new LOT (in LOT2-5) unless (i) it falls inside LOT_(N-1)'s applicable window (30d for MED/AUTO-started LOTs, 1d for ALLO-started LOTs, 45d for CART-started LOTs) or (ii) it is on/before sct_tandem_days (180d) after the immediately prior AUTO (planned tandem). Scope: LOT2-5 only. LOT1 retains the protocol convention that the first AUTO is part of induction (lot_program.R:1300-1309 unchanged). Tandem range is &lt;= 180 only (no lower bound) - see Q9 resolution. Code implemented in lot2_5_base.R: auto_cand CTE and lot_n_sct ENDING_AUTO_DT now apply the window-by-type rule; prev_end CTE pulls PREV_START_DT and PREV_START_TYPE from lot_long for the window lookup.</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -5205,7 +5205,7 @@
   d_MED   = first non-steroid MM agent MAP_START_DT (excl. permissible biosimilar subs)
   d_ALLO  = first ALLO SCT date
   d_CART  = first CAR-T infusion date (FIRST_CART_DT)
-  d_AUTO  = first AUTO date (Q16, 06-May): triggers LOT_(N+1) unless (i) it falls inside LOT_N's applicable window from LOT_N_START_DT (30d for MED/AUTO-started LOTs, 1d for ALLO-started, 45d for CART-started) or (ii) it is 60-180 days after the immediately prior AUTO (planned tandem). First-ever AUTOs CAN trigger a new LOT (LOT2-5 only; LOT1 retains the protocol convention that the first AUTO is part of induction).</t>
+  d_AUTO  = first AUTO date (Q16, 06-May): triggers LOT_(N+1) unless (i) it falls inside LOT_N's applicable window from LOT_N_START_DT (30d for MED/AUTO-started LOTs, 1d for ALLO-started, 45d for CART-started) or (ii) it is on/before sct_tandem_days (180d) after the immediately prior AUTO (planned tandem). First-ever AUTOs CAN trigger a new LOT (LOT2-5 only; LOT1 retains the protocol convention that the first AUTO is part of induction).</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Planned tandem (60-180d after a prior AUTO) is a CONTINUATION and is NOT a candidate.</t>
+          <t>Planned tandem (within sct_tandem_days = 180d of a prior AUTO) is a CONTINUATION and is NOT a candidate. Per Q9 resolution: no &lt;60d lower bound enforced (matches LOT1).</t>
         </is>
       </c>
     </row>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -4470,17 +4470,17 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Draft (current code): DISCONTINUATION - CAR-T LOT spans through last consolidation MAP_END_DT and routes by runout. Alternative: force SCT_CART for any CAR-T-started LOT regardless of how the consolidation regimen ends.</t>
+          <t>RESOLVED per Onkar 13-May: DISCONTINUATION (current code). Rationale: SCT_CART describes how the LOT STARTED, not how it ended. When the consolidation regimen runs out of supply, the LOT ended because the meds stopped - that is DISCONTINUATION. The CAR-T LOT spans through last consolidation MAP_END_DT and routes the end reason by runout exactly like any other LOT.</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Julia / Onkar</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -1638,7 +1638,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Two AUTOs &gt;=60 and &lt;=180 days apart.</t>
+          <t>Two AUTOs within 180 days = planned tandem.</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Two AUTOs &lt;= sct_tandem_days (180 days) apart = planned tandem (continuation, no new LOT). Any other AUTO that falls outside LOT_(N-1)'s applicable window starts a new LOT.</t>
+          <t>Two AUTOs within 180 days = planned tandem (continuation, no new LOT). Any other AUTO that falls outside LOT N's applicable window starts a new LOT.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Same-day / overlapping-event priority (revised per Julia 06-May to keep DEATH above DISCONTINUATION): SCT_ALLO &gt; SCT_CART &gt; SCT_AUTO &gt; CART_INIT &gt; MED_ADD &gt; DEATH &gt; DISCONTINUATION &gt; STUDY_END. DEATH moved above DISCONTINUATION so patients who run out and then die within the LOT keep REASON = DEATH (the runout date is still recorded in LOTN_BASE_DISCON_DT).</t>
+          <t>Same-day / overlapping-event priority (revised per Julia 06-May to keep DEATH above DISCONTINUATION): SCT_ALLO &gt; SCT_CART &gt; SCT_AUTO &gt; CART_INIT &gt; MED_ADD &gt; DEATH &gt; DISCONTINUATION &gt; STUDY_END. DEATH outranks DISCONTINUATION so patients who run out then die keep REASON = DEATH (the runout date is still recorded in LOTN_BASE_DISCON_DT). EXCEPTION (Q1.1): if a patient runs out and then starts a new LOT trigger (new MM agent, ALLO, CART, or qualifying AUTO) before death, DISCONTINUATION wins at the runout date and the new trigger starts LOT N+1 - DEATH does not silently swallow post-runout therapy.</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Always, when MAP_START_DT is strictly after LOT_(N-1)_BASE_END_DT (i.e., outside the prior LOT's span / induction window).</t>
+          <t>Always, when the agent appears after the prior LOT's end date.</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Steroids and biosimilar subs of LOT_(N-1) drugs do not start a LOT. Code: lot2_5_base.R::med_cand uses MAP_START_DT &gt; PREV_END_DT - no gating on the prior LOT's end reason.</t>
+          <t>Starts a new LOT when a non-steroid, non-biosimilar MM agent appears after LOT_(N-1)_BASE_END_DT. The prior LOT's end reason does not matter.</t>
         </is>
       </c>
     </row>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -2861,7 +2861,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Two AUTOs within 180 days = planned tandem (continuation, no new LOT). Any other AUTO that falls outside LOT N's applicable window starts a new LOT.</t>
+          <t>AUTO claims are first grouped into transplant events in tx_auto_dates (14-day window grouping + 60-day event-separation rule). Among those derived AUTO events, a second AUTO within 180 days of the first is treated as planned tandem (continuation, no new LOT). Any other AUTO that falls outside LOT N's applicable window starts a new LOT.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Per Julia 13-May: implementation uses ONLY the upper bound. The MM protocol convention is 60-180 days, but the &lt; 60 d case is too rare and ambiguous (usually re-conditioning / salvage rather than a planned tandem) to gate on. Matches LOT1's existing behaviour. Use datediff without +1.</t>
+          <t>Per Julia 13-May: tandem classification uses ONLY the upper bound. The &lt; 60 d case is moot because tx_auto_dates upstream already merges claims &lt; 60 d apart into a single event. Matches LOT1's existing behaviour. Use datediff without +1.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr"/>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Distinct from DISCONTINUATION. Per Q1 (06-May): runout cases now correctly show DISCONTINUATION on the dashboard - DEATH / STUDY_END no longer absorb runouts that previously hid behind the 90d buffer. Per Q1.1: if a patient runs out, starts new therapy, then dies, the runout is the LOT N end (REASON = DISCONTINUATION) and the new event triggers LOT N+1 - DEATH does not silently swallow post-runout therapy. Disenrollment is NOT a primary end event.</t>
+          <t>Death and study end do not start a new LOT. If the patient runs out of regimen therapy, the LOT ends as DISCONTINUATION. If the patient starts a new MM therapy after runout, that therapy starts the next LOT. Death only becomes the end reason when no next-LOT trigger occurs first. Disenrollment is NOT a primary end event.</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>RESOLVED per Julia 13-May: keep implementation at &lt;= sct_tandem_days (180) only. Ignore the &lt; 60 day case - rare and ambiguous (usually re-conditioning / salvage, not a planned tandem). The MM protocol describes tandem as 60-180 days; this is noted in the spec but not enforced in code. Matches existing LOT1 behaviour, keeping LOT1 and LOT2-5 consistent. datediff is used without +1.</t>
+          <t>RESOLVED per Julia 13-May: tandem classification uses &lt;= sct_tandem_days (180) only. Context: AUTO claims are first grouped into transplant events in tx_auto_dates, which already applies a 14-day window grouping and a 60-day event-separation rule (cfg$sct_auto_gap_days). Claims less than 60 days apart get MERGED into a single AUTO event upstream, so by the time tandem classification runs, two distinct AUTO events are always &gt;= 60 days apart. The tandem check then only needs the upper bound: a second derived AUTO within 180 days of the first is a planned tandem. datediff used without +1. Matches LOT1's existing behaviour.</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>RESOLVED + IMPLEMENTED: AUTO starts a new LOT (in LOT2-5) unless (i) it falls inside LOT_(N-1)'s applicable window (30d for MED/AUTO-started LOTs, 1d for ALLO-started LOTs, 45d for CART-started LOTs) or (ii) it is on/before sct_tandem_days (180d) after the immediately prior AUTO (planned tandem). Scope: LOT2-5 only. LOT1 retains the protocol convention that the first AUTO is part of induction (lot_program.R:1300-1309 unchanged). Tandem range is &lt;= 180 only (no lower bound) - see Q9 resolution. Code implemented in lot2_5_base.R: auto_cand CTE and lot_n_sct ENDING_AUTO_DT now apply the window-by-type rule; prev_end CTE pulls PREV_START_DT and PREV_START_TYPE from lot_long for the window lookup.</t>
+          <t>RESOLVED + IMPLEMENTED: AUTO starts a new LOT (in LOT2-5) unless (i) it falls inside LOT_(N-1)'s applicable window (30d for MED/AUTO-started LOTs, 1d for ALLO-started LOTs, 45d for CART-started LOTs) or (ii) it is on/before sct_tandem_days (180d) after the immediately prior AUTO (planned tandem). Scope: LOT2-5 only. LOT1 retains the protocol convention that the first AUTO is part of induction (lot_program.R:1300-1309 unchanged). Tandem classification checks only the 180-day upper bound after AUTO events have been grouped upstream (see Q9 resolution). Code implemented in lot2_5_base.R: auto_cand CTE and lot_n_sct ENDING_AUTO_DT now apply the window-by-type rule; prev_end CTE pulls PREV_START_DT and PREV_START_TYPE from lot_long for the window lookup.</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Planned tandem (within sct_tandem_days = 180d of a prior AUTO) is a CONTINUATION and is NOT a candidate. Per Q9 resolution: no &lt;60d lower bound enforced (matches LOT1).</t>
+          <t>AUTO events are already grouped upstream in tx_auto_dates (14-day window + 60-day event-separation rule). Among derived AUTO events, a second AUTO within 180 days of the first is a planned tandem (CONTINUATION, not a candidate).</t>
         </is>
       </c>
     </row>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -4092,7 +4092,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>RESOLVED + IMPLEMENTED. Reply to Julia (06-May comments 2c + 4c): Removing the LOT-level 90d confirmation gap from both LOT1 and LOT2-5 per your request. LOTN_BASE_DISCON_DT will always equal the last med date (max MAP_END_DT across induction agents) whenever a runout exists - no observation-time buffer. To preserve the death signal, end-reason priority is flipped so DEATH &gt; DISCONTINUATION &gt; STUDY_END (was DISCONTINUATION &gt; DEATH &gt; STUDY_END). Edge-case refinement (Q1.1): DEATH only preempts DISCONTINUATION when no LOT-(N+1)-qualifying trigger exists in (DISCON_DT, OBS_END_DT]. If the patient ran out, started new therapy (or had an SCT), and then died, the runout is the true LOT N end (REASON = DISCONTINUATION) and the new event triggers LOT N+1 in the next iteration - prevents post-runout therapy from being silently swallowed by death. Effect: (1) runs out, dies, no post-runout therapy =&gt; REASON = DEATH at death date; (2) runs out, starts new therapy, then dies =&gt; REASON = DISCONTINUATION at runout; new therapy starts LOT N+1; (3) runs out, reaches study end =&gt; REASON = DISCONTINUATION at runout (matches dashboard expectation); (4) runout date is still recorded in LOTN_BASE_DISCON_DT even when REASON = DEATH. MAP-level discontinuation gap (map_discon_gap_days, per-drug) is UNCHANGED.</t>
+          <t>IMPLEMENTED; trade-off awaiting explicit confirmation from Julia. Per Julia 06-May comments 2c + 4c: removed the LOT-level 90d confirmation gap from both LOT1 and LOT2-5. LOTN_BASE_DISCON_DT now equals the last med date (max MAP_END_DT across induction agents) whenever a runout exists and falls on/before OBS_END_DT - no observation-time buffer. End-reason priority flipped to DEATH &gt; DISCONTINUATION &gt; STUDY_END to preserve the death signal (was DISCONTINUATION &gt; DEATH &gt; STUDY_END). Edge-case refinement (Q1.1): DEATH only preempts DISCONTINUATION when no LOT-(N+1)-qualifying trigger exists in (DISCON_DT, OBS_END_DT] - prevents post-runout therapy from being silently swallowed by death. TRADE-OFF (not surfaced by the original spec row; flagging for explicit Julia confirmation): Removing the buffer commits to a DISCONTINUATION label at the runout date for ALL patients with a runout, including those observed for less than 90 days afterward. Such short-follow-up patients could in principle have restarted therapy beyond their observation window; the prior buffer was the mechanism that left their LOT label uncommitted (as STUDY_END) until 90 d of post-runout observation accumulated. Direction of bias: may over-label DISCONTINUATION for late-enrolled / short-FU patients. Aligns with 'runout = DISCONTINUATION'; diverges from 'wait until confirmed' semantics. MAP-level per-drug gap (map_discon_gap_days) is UNCHANGED. Effect summary: (1) runs out, dies, no post-runout therapy =&gt; REASON = DEATH at death date; (2) runs out, starts new therapy, then dies =&gt; REASON = DISCONTINUATION at runout; new therapy starts LOT N+1; (3) runs out, reaches study end with &gt;=90d post-runout obs =&gt; REASON = DISCONTINUATION at runout (matches dashboard expectation); (4) runs out, reaches study end with &lt;90d post-runout obs =&gt; REASON = DISCONTINUATION at runout (was STUDY_END at obs end pre-fix); (5) runout date is still recorded in LOTN_BASE_DISCON_DT even when REASON = DEATH.</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Pending confirmation</t>
         </is>
       </c>
     </row>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -2597,7 +2597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>T_MEDICAL: FST_DT + medical_day_supply - 1. T_RX: FILL_DT + DAYS_SUP - 1. Missing DAY_SUPPLY -&gt; 28d default (do not delete claims). No LOT-level 90d observation buffer (removed per Julia 06-May).</t>
+          <t>T_MEDICAL: FST_DT + medical_day_supply - 1. T_RX: FILL_DT + DAYS_SUP - 1. Missing DAY_SUPPLY -&gt; 28d default (do not delete claims). There is only ONE 90-day rule in the pipeline: the MAP-level per-drug rule (map_discon_gap_days). It says a drug is discontinued if there is no refill within 90 days. There is no additional LOT-level wait on top of that.</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr"/>
@@ -2774,34 +2774,30 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>LOT_DISCON_GAP_DAYS</t>
+          <t>ALLO_ALWAYS_ENDS_LOT</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>LOT-level discontinuation buffer (days)</t>
+          <t>ALLO always ends current LOT</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>REMOVED per Julia 06-May ('we are not using the 90d gap rule'). LOTN_BASE_DISCON_DT = last med date (max MAP_END_DT) whenever a runout exists; no observation-time buffer. Per-drug discontinuation detection still uses MAP-level map_discon_gap_days (unchanged).</t>
+          <t>Any ALLO ends current LOT day before ALLO, and starts a new ALLO LOT.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Applies to both LOT1 and LOT2-5.</t>
-        </is>
-      </c>
+          <t>CL_SCT_CODELIST (ALLO)</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr"/>
       <c r="H5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
@@ -2812,30 +2808,34 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ALLO_ALWAYS_ENDS_LOT</t>
+          <t>AUTO_TANDEM_WINDOW</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>ALLO always ends current LOT</t>
+          <t>Tandem AUTO window</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>&lt;= 180 days</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Any ALLO ends current LOT day before ALLO, and starts a new ALLO LOT.</t>
+          <t>AUTO claims are first grouped into transplant events in tx_auto_dates (14-day window grouping + 60-day event-separation rule). Among those derived AUTO events, a second AUTO within 180 days of the first is treated as planned tandem (continuation, no new LOT). Any other AUTO that falls outside LOT N's applicable window starts a new LOT.</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>CL_SCT_CODELIST (ALLO)</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr"/>
+          <t>CL_SCT_CODELIST (AUTO)</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Per Julia 13-May: tandem classification uses ONLY the upper bound. The &lt; 60 d case is moot because tx_auto_dates upstream already merges claims &lt; 60 d apart into a single event. Matches LOT1's existing behaviour. Use datediff without +1.</t>
+        </is>
+      </c>
       <c r="H6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
@@ -2846,32 +2846,32 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>AUTO_TANDEM_WINDOW</t>
+          <t>CART_CONSOLIDATION_DAYS</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Tandem AUTO window</t>
+          <t>CAR-T consolidation window</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>&lt;= 180 days</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>AUTO claims are first grouped into transplant events in tx_auto_dates (14-day window grouping + 60-day event-separation rule). Among those derived AUTO events, a second AUTO within 180 days of the first is treated as planned tandem (continuation, no new LOT). Any other AUTO that falls outside LOT N's applicable window starts a new LOT.</t>
+          <t>Agents within 45 days of FIRST_CART_DT are consolidated into the CAR-T LOT (study-team decision).</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>CL_SCT_CODELIST (AUTO)</t>
+          <t>CL_SCT_CODELIST (CART)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Per Julia 13-May: tandem classification uses ONLY the upper bound. The &lt; 60 d case is moot because tx_auto_dates upstream already merges claims &lt; 60 d apart into a single event. Matches LOT1's existing behaviour. Use datediff without +1.</t>
+          <t>Do NOT advance to LOT_(N+1) for consolidated agents.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr"/>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>CART_CONSOLIDATION_DAYS</t>
+          <t>LOTN_BASE_END_DT</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>CAR-T consolidation window</t>
+          <t>Final LOT N end date (PRIMARY)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Agents within 45 days of FIRST_CART_DT are consolidated into the CAR-T LOT (study-team decision).</t>
+          <t>Earliest qualifying end event from LOTN_END_DT_TEMP. Also: CART_INIT applies when a CAR-T infusion occurs within 45 days of the first new agent that breaks LOT N.</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>CL_SCT_CODELIST (CART)</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Do NOT advance to LOT_(N+1) for consolidated agents.</t>
+          <t>ALLO LOT spans a single day, start = end = ALLO_DT. CAR-T LOT spans through last consolidation MAP_END_DT.</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
@@ -2922,22 +2922,22 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_DT</t>
+          <t>LOTN_BASE_END_REASON</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Final LOT N end date (PRIMARY)</t>
+          <t>Final LOT N end reason (PRIMARY)</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>SCT_ALLO / SCT_CART / SCT_AUTO / CART_INIT / MED_ADD / DEATH / DISCONTINUATION / STUDY_END</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Earliest qualifying end event from LOTN_END_DT_TEMP. Also: CART_INIT applies when a CAR-T infusion occurs within 45 days of the first new agent that breaks LOT N.</t>
+          <t>Reason corresponding to LOTN_BASE_END_DT. DISENROLLMENT only in sensitivity (see *_CE_SENS).</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>ALLO LOT spans a single day, start = end = ALLO_DT. CAR-T LOT spans through last consolidation MAP_END_DT.</t>
+          <t>Same-day / overlapping-event priority (revised per Julia 06-May to keep DEATH above DISCONTINUATION): SCT_ALLO &gt; SCT_CART &gt; SCT_AUTO &gt; CART_INIT &gt; MED_ADD &gt; DEATH &gt; DISCONTINUATION &gt; STUDY_END. DEATH outranks DISCONTINUATION so patients who run out then die keep REASON = DEATH (the runout date is still recorded in LOTN_BASE_DISCON_DT). EXCEPTION (Q1.1): if a patient runs out and then starts a new LOT trigger (new MM agent, ALLO, CART, or qualifying AUTO) before death, DISCONTINUATION wins at the runout date and the new trigger starts LOT N+1 - DEATH does not silently swallow post-runout therapy.</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr"/>
@@ -2960,32 +2960,32 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_REASON</t>
+          <t>LOTN_BASE_END_DT_CE_SENS</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Final LOT N end reason (PRIMARY)</t>
+          <t>LOT N end date (SENSITIVITY)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>SCT_ALLO / SCT_CART / SCT_AUTO / CART_INIT / MED_ADD / DEATH / DISCONTINUATION / STUDY_END</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Reason corresponding to LOTN_BASE_END_DT. DISENROLLMENT only in sensitivity (see *_CE_SENS).</t>
+          <t>Same as LOTN_BASE_END_DT, additionally capped at ELIGEND. Emitted when CENSOR_AT_DISENROLLMENT = TRUE.</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>T_MEMBER_CONT_ENROLLMENT</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Same-day / overlapping-event priority (revised per Julia 06-May to keep DEATH above DISCONTINUATION): SCT_ALLO &gt; SCT_CART &gt; SCT_AUTO &gt; CART_INIT &gt; MED_ADD &gt; DEATH &gt; DISCONTINUATION &gt; STUDY_END. DEATH outranks DISCONTINUATION so patients who run out then die keep REASON = DEATH (the runout date is still recorded in LOTN_BASE_DISCON_DT). EXCEPTION (Q1.1): if a patient runs out and then starts a new LOT trigger (new MM agent, ALLO, CART, or qualifying AUTO) before death, DISCONTINUATION wins at the runout date and the new trigger starts LOT N+1 - DEATH does not silently swallow post-runout therapy.</t>
+          <t>Primary LOTN_BASE_END_DT untouched.</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
@@ -2998,32 +2998,32 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_DT_CE_SENS</t>
+          <t>LOTN_BASE_END_REASON_CE_SENS</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>LOT N end date (SENSITIVITY)</t>
+          <t>LOT N end reason (SENSITIVITY)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>(primary set) + DISENROLLMENT</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Same as LOTN_BASE_END_DT, additionally capped at ELIGEND. Emitted when CENSOR_AT_DISENROLLMENT = TRUE.</t>
+          <t>Same as primary, plus DISENROLLMENT when ELIGEND binds.</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>T_MEMBER_CONT_ENROLLMENT</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Primary LOTN_BASE_END_DT untouched.</t>
+          <t>REQUIRED: emit DISENROLLMENT (do NOT collapse to STUDY_END). Diverges from current LOT1 behaviour.</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr"/>
@@ -3036,22 +3036,22 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_REASON_CE_SENS</t>
+          <t>LOTN_BASE_LENGTH</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>LOT N end reason (SENSITIVITY)</t>
+          <t>LOT N duration (days)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>(primary set) + DISENROLLMENT</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Same as primary, plus DISENROLLMENT when ELIGEND binds.</t>
+          <t>If reason = DISCONTINUATION: LOTN_BASE_DISCON_DT - LOTN_START_DT + 1. Else: LOTN_BASE_END_DT - LOTN_START_DT + 1.</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -3061,106 +3061,90 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>REQUIRED: emit DISENROLLMENT (do NOT collapse to STUDY_END). Diverges from current LOT1 behaviour.</t>
+          <t>Confirm censored handling (LOT1 M1).</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr"/>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>FU_PD</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>LOTN_BASE_LENGTH</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>LOT N duration (days)</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>If reason = DISCONTINUATION: LOTN_BASE_DISCON_DT - LOTN_START_DT + 1. Else: LOTN_BASE_END_DT - LOTN_START_DT + 1.</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Confirm censored handling (LOT1 M1).</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>WORKED EXAMPLE D - End-reason priority with CART_INIT</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>LOT3 starts 2025-11-01 (KRd). Competing events: run-out 2026-04-15; POMA add 2026-03-20; CAR-T 2026-04-02 (within 45d of POMA); death 2026-05-20. Priority resolves to CART_INIT.</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="10" t="n"/>
-      <c r="H17" s="11" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="11" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Value for this patient</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>How it was derived</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>Value for this patient</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>How it was derived</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="12" t="n"/>
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>LOTN_BASE_END_DT</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>FIRST_CART_DT - 1.</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_DT</t>
+          <t>LOTN_BASE_END_REASON</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>CART_INIT</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>FIRST_CART_DT - 1.</t>
+          <t>CART_INIT outranks MED_ADD; CAR-T within 45d of first add.</t>
         </is>
       </c>
       <c r="D19" s="9" t="n"/>
@@ -3172,17 +3156,17 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_REASON</t>
+          <t>LOTN_BASE_LENGTH</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>CART_INIT</t>
+          <t>152</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>CART_INIT outranks MED_ADD; CAR-T within 45d of first add.</t>
+          <t>2026-04-01 - 2025-11-01 + 1.</t>
         </is>
       </c>
       <c r="D20" s="9" t="n"/>
@@ -3194,17 +3178,17 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_LENGTH</t>
+          <t>LOT_(N+1)_START_DT</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>2026-04-01 - 2025-11-01 + 1.</t>
+          <t>LOT4_START_TYPE = CART.</t>
         </is>
       </c>
       <c r="D21" s="9" t="n"/>
@@ -3213,75 +3197,75 @@
       <c r="G21" s="9" t="n"/>
       <c r="H21" s="9" t="n"/>
     </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>LOT_(N+1)_START_DT</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>LOT4_START_TYPE = CART.</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>WORKED EXAMPLE E - Discontinuation (run-out)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>LOT2 starts 2025-08-20 (DARA+LENA). Last LENA MAP_END_DT 2026-02-06; last DARA 2026-01-15. No new agent, no death, study continues.</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="n"/>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="10" t="n"/>
-      <c r="H26" s="11" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="11" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Value for this patient</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>How it was derived</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>Value for this patient</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>How it was derived</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="12" t="n"/>
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>LOTN_BASE_DISCON_DT</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>max(MAP_END_DT) across LOT2 induction agents (last med date).</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="9" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_DISCON_DT</t>
+          <t>LOTN_BASE_END_DT</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -3291,7 +3275,7 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>max(MAP_END_DT) across LOT2 induction agents (last med date).</t>
+          <t>Runout = LOT end. The only 90-day rule is the per-drug MAP-level one; there is no separate LOT-level wait.</t>
         </is>
       </c>
       <c r="D28" s="9" t="n"/>
@@ -3303,17 +3287,17 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_DT</t>
+          <t>LOTN_BASE_END_REASON</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>DISCONTINUATION</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Runout = LOT end (no LOT-level 90d buffer).</t>
+          <t>Runout reached; no death or higher-priority event.</t>
         </is>
       </c>
       <c r="D29" s="9" t="n"/>
@@ -3325,17 +3309,17 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_REASON</t>
+          <t>LOTN_BASE_LENGTH</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>DISCONTINUATION</t>
+          <t>171</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Runout reached; no death or higher-priority event.</t>
+          <t>2026-02-06 - 2025-08-20 + 1.</t>
         </is>
       </c>
       <c r="D30" s="9" t="n"/>
@@ -3344,87 +3328,83 @@
       <c r="G30" s="9" t="n"/>
       <c r="H30" s="9" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>LOTN_BASE_LENGTH</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>2026-02-06 - 2025-08-20 + 1.</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>WORKED EXAMPLE F - Disenrollment primary vs sensitivity</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>LOT4 starts 2026-01-05. ELIGEND 2026-04-30; no death; study_end 2026-12-31.</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="10" t="n"/>
-      <c r="H35" s="11" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="11" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Value for this patient</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>How it was derived</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="12" t="n"/>
+      <c r="H35" s="12" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>Value for this patient</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>How it was derived</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="n"/>
-      <c r="E36" s="12" t="n"/>
-      <c r="F36" s="12" t="n"/>
-      <c r="G36" s="12" t="n"/>
-      <c r="H36" s="12" t="n"/>
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>LOTN_BASE_END_DT (PRIMARY)</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Disenrollment ignored; min(death, study_end) = study_end.</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_DT (PRIMARY)</t>
+          <t>LOTN_BASE_END_REASON (PRIMARY)</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>Disenrollment ignored; min(death, study_end) = study_end.</t>
-        </is>
-      </c>
+          <t>STUDY_END</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr"/>
       <c r="D37" s="9" t="n"/>
       <c r="E37" s="9" t="n"/>
       <c r="F37" s="9" t="n"/>
@@ -3434,15 +3414,19 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_REASON (PRIMARY)</t>
+          <t>LOTN_BASE_END_DT_CE_SENS</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>STUDY_END</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr"/>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>ELIGEND binds.</t>
+        </is>
+      </c>
       <c r="D38" s="9" t="n"/>
       <c r="E38" s="9" t="n"/>
       <c r="F38" s="9" t="n"/>
@@ -3452,17 +3436,17 @@
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_DT_CE_SENS</t>
+          <t>LOTN_BASE_END_REASON_CE_SENS</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>DISENROLLMENT</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>ELIGEND binds.</t>
+          <t>Required: do NOT collapse to STUDY_END.</t>
         </is>
       </c>
       <c r="D39" s="9" t="n"/>
@@ -3474,17 +3458,17 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_END_REASON_CE_SENS</t>
+          <t>LOTN_BASE_LENGTH (PRIMARY)</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>DISENROLLMENT</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Required: do NOT collapse to STUDY_END.</t>
+          <t>2026-12-31 - 2026-01-05 + 1.</t>
         </is>
       </c>
       <c r="D40" s="9" t="n"/>
@@ -3496,17 +3480,17 @@
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>LOTN_BASE_LENGTH (PRIMARY)</t>
+          <t>LOTN_BASE_LENGTH_CE_SENS</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>116</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>2026-12-31 - 2026-01-05 + 1.</t>
+          <t>2026-04-30 - 2026-01-05 + 1.</t>
         </is>
       </c>
       <c r="D41" s="9" t="n"/>
@@ -3515,51 +3499,29 @@
       <c r="G41" s="9" t="n"/>
       <c r="H41" s="9" t="n"/>
     </row>
-    <row r="42">
-      <c r="A42" s="13" t="inlineStr">
-        <is>
-          <t>LOTN_BASE_LENGTH_CE_SENS</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-30 - 2026-01-05 + 1.</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="n"/>
-      <c r="E42" s="9" t="n"/>
-      <c r="F42" s="9" t="n"/>
-      <c r="G42" s="9" t="n"/>
-      <c r="H42" s="9" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="23">
     <mergeCell ref="C41:H41"/>
-    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="C40:H40"/>
-    <mergeCell ref="C31:H31"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C36:H36"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="C27:H27"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="C39:H39"/>
-    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C38:H38"/>
     <mergeCell ref="C19:H19"/>
-    <mergeCell ref="C38:H38"/>
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="C37:H37"/>
+    <mergeCell ref="A33:H33"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="C30:H30"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="C26:H26"/>
     <mergeCell ref="C29:H29"/>
     <mergeCell ref="A34:H34"/>
   </mergeCells>
@@ -4087,12 +4049,12 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>90-day discontinuation gap - keep, or remove?</t>
+          <t>Is there a 90-day LOT-level discontinuation buffer?</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>IMPLEMENTED; trade-off awaiting explicit confirmation from Julia. Per Julia 06-May comments 2c + 4c: removed the LOT-level 90d confirmation gap from both LOT1 and LOT2-5. LOTN_BASE_DISCON_DT now equals the last med date (max MAP_END_DT across induction agents) whenever a runout exists and falls on/before OBS_END_DT - no observation-time buffer. End-reason priority flipped to DEATH &gt; DISCONTINUATION &gt; STUDY_END to preserve the death signal (was DISCONTINUATION &gt; DEATH &gt; STUDY_END). Edge-case refinement (Q1.1): DEATH only preempts DISCONTINUATION when no LOT-(N+1)-qualifying trigger exists in (DISCON_DT, OBS_END_DT] - prevents post-runout therapy from being silently swallowed by death. TRADE-OFF (not surfaced by the original spec row; flagging for explicit Julia confirmation): Removing the buffer commits to a DISCONTINUATION label at the runout date for ALL patients with a runout, including those observed for less than 90 days afterward. Such short-follow-up patients could in principle have restarted therapy beyond their observation window; the prior buffer was the mechanism that left their LOT label uncommitted (as STUDY_END) until 90 d of post-runout observation accumulated. Direction of bias: may over-label DISCONTINUATION for late-enrolled / short-FU patients. Aligns with 'runout = DISCONTINUATION'; diverges from 'wait until confirmed' semantics. MAP-level per-drug gap (map_discon_gap_days) is UNCHANGED. Effect summary: (1) runs out, dies, no post-runout therapy =&gt; REASON = DEATH at death date; (2) runs out, starts new therapy, then dies =&gt; REASON = DISCONTINUATION at runout; new therapy starts LOT N+1; (3) runs out, reaches study end with &gt;=90d post-runout obs =&gt; REASON = DISCONTINUATION at runout (matches dashboard expectation); (4) runs out, reaches study end with &lt;90d post-runout obs =&gt; REASON = DISCONTINUATION at runout (was STUDY_END at obs end pre-fix); (5) runout date is still recorded in LOTN_BASE_DISCON_DT even when REASON = DEATH.</t>
+          <t>RESOLVED: NO. There is only ONE 90-day rule in the pipeline - the MAP-level per-drug rule (map_discon_gap_days). A drug is considered discontinued if no refill appears within 90 days. There is NO additional LOT-level 90-day wait on top of that. Once all base meds run out, the LOT ends at that runout date directly. Confirmed by Julia 13-May: ship as-is with 'runout = DISCONTINUATION' semantics. Direction of the labeling change is acknowledged: patients with &lt; 90 d of post-runout observation are now labeled DISCONTINUATION at the runout date rather than STUDY_END at obs end - aligns with the intuitive reading of the data. Two follow-up adjustments to keep the cascade correct: (a) End-reason priority is DEATH &gt; DISCONTINUATION &gt; STUDY_END so patients who run out and then die still get REASON = DEATH. (b) Q1.1: DEATH preempts DISCONTINUATION only when no LOT-(N+1) trigger sits between runout and death - protects post-runout therapy from being silently absorbed by death.</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -4102,7 +4064,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>Pending confirmation</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>45d (Apr 22 decision; Q11 resolved).</t>
+          <t>45 days; study-team decision.</t>
         </is>
       </c>
     </row>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -1314,7 +1314,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>Source: T_MEDICAL (PROC_CD, BILL_PROC_CD, NDC), T_RX (NDC). Steroids excluded (MAP_MED_CLASS != 'STEROID'). LOT2-5 only; LOT1 retains protocol convention that first AUTO is part of induction.</t>
+          <t>Source: T_MEDICAL (PROC_CD, NDC), T_RX (NDC). Steroids excluded (MAP_MED_CLASS != 'STEROID'). LOT2-5 only; LOT1 retains protocol convention that first AUTO is part of induction.</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr"/>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -1314,7 +1314,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>Source: T_MEDICAL (PROC_CD, NDC), T_RX (NDC). Steroids excluded (MAP_MED_CLASS != 'STEROID'). LOT2-5 only; LOT1 retains protocol convention that first AUTO is part of induction.</t>
+          <t>Source: T_MEDICAL (PROC_CD, BILL_PROC_CD, NDC), T_RX (NDC). Steroids excluded (MAP_MED_CLASS != 'STEROID'). LOT2-5 only; LOT1 retains protocol convention that first AUTO is part of induction.</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr"/>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -2761,7 +2761,7 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Check permissible_subs before classifying as new add.</t>
+          <t>Audit / debug output column (emitted to LOT_LONG), not a primary analysis variable. Check permissible_subs before classifying as a new add.</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr"/>
@@ -2818,12 +2818,12 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>&lt;= 180 days</t>
+          <t>&lt; 60d: same event; 60-180d: tandem; &gt; 180d: new LOT</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>AUTO claims are first grouped into transplant events in tx_auto_dates (14-day window grouping + 60-day event-separation rule). Among those derived AUTO events, a second AUTO within 180 days of the first is treated as planned tandem (continuation, no new LOT). Any other AUTO that falls outside LOT N's applicable window starts a new LOT.</t>
+          <t>AUTO claims are first grouped into discrete transplant events in tx_auto_dates. Two AUTO claims/events LESS THAN 60 days apart are treated as the SAME AUTO event - they do not create a tandem flag and do not trigger a new LOT. Among distinct AUTO events: a second AUTO 60-180 days after the first is a planned tandem (continuation, same LOT, no new trigger); an AUTO more than 180 days after the prior AUTO is unplanned and starts a new LOT if it also falls outside LOT N's applicable window.</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Per Julia 13-May: tandem classification uses ONLY the upper bound. The &lt; 60 d case is moot because tx_auto_dates upstream already merges claims &lt; 60 d apart into a single event. Matches LOT1's existing behaviour. Use datediff without +1.</t>
+          <t>Per Julia 13-May: the &lt; 60 d merge is handled upstream in tx_auto_dates (sct_auto_gap_days = 60), so tandem classification only needs the &lt;= 180 d (sct_tandem_days) upper bound. Matches LOT1's existing behaviour. Use datediff without +1.</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>ALLO LOT spans a single day, start = end = ALLO_DT. CAR-T LOT spans through last consolidation MAP_END_DT.</t>
+          <t>ALLO LOT spans a single day, start = end = ALLO_DT. CAR-T LOT spans through last consolidation MAP_END_DT. Under CART_INIT the pre-CAR-T bridge agent is consolidated into the CAR-T LOT and does not create a separate non-CAR-T LOT.</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
@@ -3638,7 +3638,7 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>45-day consolidation window (study-team decision).</t>
+          <t>45-day consolidation window (study-team decision). When CART_INIT applies, the pre-CAR-T bridge agent only identifies the transition into the CAR-T LOT; it does NOT create a separate non-CAR-T LOT (do not advance to LOT_(N+1) for consolidated agents).</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>First-ever AUTOs CAN trigger a new LOT (LOT2-5 only). LOT1 keeps protocol convention that the first AUTO is part of induction.</t>
+          <t>First-ever AUTOs CAN trigger a new LOT (LOT2-5 only). LOT1 keeps protocol convention that the first AUTO is part of induction. AUTO claims &lt; 60 days apart are merged into a single AUTO event upstream (tx_auto_dates, sct_auto_gap_days = 60) and never count as a separate trigger or as a tandem.</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Always, when the agent appears after the prior LOT's end date.</t>
+          <t>Always, when the agent appears after LOT_(N-1)_BASE_END_DT (i.e. after the prior LOT's applicable induction/consolidation window) and no higher-priority SCT/CAR-T event shares that start date.</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Starts a new LOT when a non-steroid, non-biosimilar MM agent appears after LOT_(N-1)_BASE_END_DT. The prior LOT's end reason does not matter.</t>
+          <t>Starts a new LOT when a non-steroid, non-biosimilar MM agent appears after LOT_(N-1)_BASE_END_DT, regardless of the prior LOT's end reason. Same-day start priority still applies: SCT_ALLO &gt; CART &gt; SCT_AUTO &gt; MED.</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3945,49 +3945,66 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>S8. Biosimilar swap in LOT2</t>
+          <t>S7b. AUTO claims &lt; 60 days apart</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>DARA -&gt; DARA biosimilar.</t>
+          <t>Two AUTO claims/events 40 days apart during LOT2.</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>LOT does not advance.</t>
+          <t>Merged into a single AUTO event upstream (tx_auto_dates, sct_auto_gap_days=60). Not a tandem (AUTO_TAND_FLG=0) and not a new LOT trigger.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>S9. ALLO LOT span</t>
+          <t>S8. Biosimilar swap in LOT2</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>ALLO with no follow-on therapy.</t>
+          <t>DARA -&gt; DARA biosimilar.</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Single-day ALLO LOT: start = end = ALLO_DT.</t>
+          <t>LOT does not advance.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>S9. ALLO LOT span</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>ALLO with no follow-on therapy.</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Single-day ALLO LOT: start = end = ALLO_DT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
           <t>S10. CART_INIT carryover</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>CAR-T within 45 days of the first new drug add that breaks LOT1.</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>LOT1 ends with CART_INIT (LOT1 spec). LOT2_START_TYPE = CART.</t>
         </is>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -2823,7 +2823,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>AUTO claims are first grouped into discrete transplant events in tx_auto_dates. Two AUTO claims/events LESS THAN 60 days apart are treated as the SAME AUTO event - they do not create a tandem flag and do not trigger a new LOT. Among distinct AUTO events: a second AUTO 60-180 days after the first is a planned tandem (continuation, same LOT, no new trigger); an AUTO more than 180 days after the prior AUTO is unplanned and starts a new LOT if it also falls outside LOT N's applicable window.</t>
+          <t>AUTO claims are first grouped into discrete transplant events in tx_auto_dates. Two AUTO claims/events LESS THAN 60 days apart are treated as the SAME AUTO event - the near-duplicate is not a separate AUTO event, so it forms no tandem pairing and is not a separate trigger (the retained single AUTO event is still evaluated by the normal trigger rule). Among distinct AUTO events: a second AUTO 60-180 days after the first is a planned tandem (continuation, same LOT, no new trigger); an AUTO more than 180 days after the prior AUTO is unplanned and starts a new LOT if it also falls outside LOT N's applicable window.</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>ALLO LOT spans a single day, start = end = ALLO_DT. CAR-T LOT spans through last consolidation MAP_END_DT. Under CART_INIT the pre-CAR-T bridge agent is consolidated into the CAR-T LOT and does not create a separate non-CAR-T LOT.</t>
+          <t>ALLO LOT spans a single day, start = end = ALLO_DT. CAR-T LOT spans through last consolidation MAP_END_DT. Under CART_INIT the pre-CAR-T bridge agent only marks the CART_INIT transition (LOT N ends at FIRST_CART_DT - 1); it does NOT create a separate non-CAR-T LOT and is NOT carried into the CAR-T LOT regimen (CAR-T induction meds use MAP_START_DT &gt;= FIRST_CART_DT).</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Always, when the agent appears after LOT_(N-1)_BASE_END_DT (i.e. after the prior LOT's applicable induction/consolidation window) and no higher-priority SCT/CAR-T event shares that start date.</t>
+          <t>Always, when the agent appears strictly after LOT_(N-1)_BASE_END_DT (the prior LOT has ended; for medication-driven transitions the agent must also fall outside the prior LOT's induction/consolidation window) and no higher-priority SCT/CAR-T event shares that start date.</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Merged into a single AUTO event upstream (tx_auto_dates, sct_auto_gap_days=60). Not a tandem (AUTO_TAND_FLG=0) and not a new LOT trigger.</t>
+          <t>Merged into a single AUTO event upstream (tx_auto_dates, sct_auto_gap_days=60). The near-duplicate is not a separate AUTO event: no tandem (AUTO_TAND_FLG=0) and not a separate trigger; the retained single event is still evaluated by the normal AUTO trigger rule.</t>
         </is>
       </c>
     </row>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>Sequential index of the line of therapy after LOT1. LOT2 starts after LOT1 ends; LOT3 after LOT2; etc., up to LOT5.</t>
+          <t>LOT number after LOT1, up to LOT5. Each LOT starts after the previous one ends.</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>Derived sequentially. LOT_(N+1)_START_DT must be &gt; LOT_N_BASE_END_DT.</t>
+          <t>LOT_(N+1)_START_DT must be &gt; LOT_N_BASE_END_DT.</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr"/>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>Earliest of, after LOT_(N-1)_BASE_END_DT: (a) first non-steroid MM oncology agent; (b) first ALLO SCT; (c) first CAR-T infusion; (d) first AUTO SCT, EXCEPT (i) when it falls inside LOT_(N-1)'s applicable window (30d for MED/AUTO-started LOTs, 1d for ALLO-started LOTs, 45d for CART-started LOTs) or (ii) when it is on/before sct_tandem_days (180d) after the immediately prior AUTO (planned tandem - continuation, not a trigger). Permissible biosimilar substitutions do not trigger.</t>
+          <t>First of these after LOT_(N-1) ends: (a) a new non-steroid MM drug; (b) an ALLO SCT; (c) a CAR-T infusion; (d) an AUTO SCT - but an AUTO does NOT start a LOT if it is inside LOT_(N-1)'s window (30d MED/AUTO, 1d ALLO, 45d CART) or is a planned tandem (&lt;=180d after the prior AUTO). Biosimilar swaps never trigger.</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>Source: T_MEDICAL (PROC_CD, BILL_PROC_CD, NDC), T_RX (NDC). Steroids excluded (MAP_MED_CLASS != 'STEROID'). LOT2-5 only; LOT1 retains protocol convention that first AUTO is part of induction.</t>
+          <t>From T_MEDICAL / T_RX. Steroids excluded. LOT2-5 only; in LOT1 the first AUTO is induction.</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr"/>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Type of the earliest qualifying trigger.</t>
+          <t>Type of the trigger.</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Same-day tie-break (Q14 resolved, inherits LOT1): SCT_ALLO &gt; CART &gt; SCT_AUTO &gt; MED.</t>
+          <t>Same-day tie-break: SCT_ALLO &gt; CART &gt; SCT_AUTO &gt; MED.</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr"/>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Window for identifying LOT N regimen. (LOT1 uses 60.) If the patient is right-censored before the end of the 30-day window, the window closes at the censor date.</t>
+          <t>Window for picking up the LOT N regimen (LOT1 uses 60). Closes early if the patient is censored first.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>MAP_START_DT in [LOTN_START_DT, min(LOTN_START_DT + 29, OBS_END_DT)] = induction.</t>
+          <t>Induction = MAP_START_DT in [LOTN_START_DT, min(LOTN_START_DT + 29, OBS_END_DT)].</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr"/>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Non-steroid MM oncology agents within the 30-day induction window. Permissible biosimilar substitutions do not advance the regimen.</t>
+          <t>Non-steroid MM drugs in the 30-day induction window. Biosimilar swaps do not change the regimen.</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Filter MAP_MED_CLASS != 'STEROID'.</t>
+          <t>Exclude steroids (MAP_MED_CLASS != 'STEROID').</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr"/>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Count of distinct MED_ABBR in LOTN_BASE_MEDS.</t>
+          <t>Number of distinct drugs in LOTN_BASE_MEDS.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>One flag column per non-steroid MED_ABBR in CL_MMA_ROLLUP (e.g. LOTN_MED_BORT, LOTN_MED_LENA, LOTN_MED_DARA, ...). = 1 if that medication is in LOTN_BASE_MEDS.</t>
+          <t>One flag per non-steroid drug (e.g. LOTN_MED_BORT, LOTN_MED_DARA). 1 if the drug is in LOTN_BASE_MEDS.</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Mirror LOT1 dynamic flag generation; steroid abbreviations excluded.</t>
+          <t>Same dynamic flags as LOT1; steroids excluded.</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>One flag column per non-steroid MED_CLASS in CL_MMA_ROLLUP (e.g. LOTN_CLASS_PROTINHIB, LOTN_CLASS_IMMUNOMOD, ...). = 1 if any LOTN_BASE_MEDS agent has that class.</t>
+          <t>One flag per non-steroid class (e.g. LOTN_CLASS_IMMUNOMOD). 1 if any LOTN_BASE_MEDS drug is in that class.</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Mirror LOT1 dynamic class flag generation.</t>
+          <t>Same as LOT1.</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Patient had &gt;=1 valid AUTO during LOT N.</t>
+          <t>1 if the patient had &gt;=1 valid AUTO during LOT N.</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Inherit LOT1 SCT logic: 14-day windowing, 60-day gap validation.</t>
+          <t>Same SCT logic as LOT1.</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>AUTO not part of a valid tandem pair.</t>
+          <t>1 if the AUTO is not part of a tandem pair.</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Two AUTOs within 180 days = planned tandem.</t>
+          <t>1 if two AUTOs are &lt;=180 days apart.</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Use datediff without +1.</t>
+          <t>datediff, no +1.</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr"/>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>DT_2 populated only if planned tandem.</t>
+          <t>DT_2 only set for a planned tandem.</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>AUTO_DT_2 if tandem else AUTO_DT_1 else NULL.</t>
+          <t>AUTO_DT_2 if tandem, else AUTO_DT_1, else NULL.</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Flag is 1 when LOT N induction has BOTH (a) &gt;=1 valid mono-maintenance agent OR a valid dual combo, AND (b) an anchor agent. Mono: LENA, BORT, DARA, IXAZ, THAL. Dual: BORT+LENA, CARF+LENA, DARA+LENA.</t>
+          <t>1 when induction has BOTH (a) a mono-maintenance drug or a valid dual combo, AND (b) an anchor drug. Mono: LENA, BORT, DARA, IXAZ, THAL. Dual: BORT+LENA, CARF+LENA, DARA+LENA.</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Descriptive flag; no standalone maintenance LOT.</t>
+          <t>Descriptive only; no separate maintenance LOT.</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr"/>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Flag is 1 when LOTN_START_TYPE = SCT_ALLO. ALLO LOT contains no MM therapies and spans a single day: start = end = ALLO_DT. ALLO is treated as a punctuation event between LOTs; the next MM agent starts the following LOT.</t>
+          <t>1 when START_TYPE = SCT_ALLO. An ALLO LOT has no MM drugs and lasts one day (start = end = ALLO_DT). The next MM drug starts the following LOT.</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Flag is 1 when LOTN_START_TYPE = CART. Agents within 45 days of FIRST_CART_DT are consolidated into LOT N (study-team decision).</t>
+          <t>1 when START_TYPE = CART. Drugs within 45 days of FIRST_CART_DT belong to this LOT.</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Do NOT advance to LOT_(N+1) for consolidated agents.</t>
+          <t>Consolidated drugs do not start LOT_(N+1).</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr"/>
@@ -1834,14 +1834,14 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>WORKED EXAMPLE A - LOT2 starts on a new medication</t>
+          <t>WORKED EXAMPLE A - LOT2 starts on a new drug</t>
         </is>
       </c>
     </row>
     <row r="21" ht="60" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>VRd in LOT1; DARA added 2025-08-20 (LOT1 ends 2025-08-19, MED_ADD). LENA refills present within 30d. No SCT/CAR-T.</t>
+          <t>VRd in LOT1; DARA added 2025-08-20 (LOT1 ends 2025-08-19). LENA refills within 30d. No SCT/CAR-T.</t>
         </is>
       </c>
       <c r="B21" s="10" t="n"/>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Earliest trigger after LOT1_BASE_END_DT (2025-08-19) = DARA.</t>
+          <t>First trigger after LOT1 ends = DARA.</t>
         </is>
       </c>
       <c r="D24" s="9" t="n"/>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>DARA + LENA is a valid dual maintenance regimen; the two agents anchor each other.</t>
+          <t>DARA+LENA is a valid maintenance pair.</t>
         </is>
       </c>
       <c r="D32" s="9" t="n"/>
@@ -2102,7 +2102,7 @@
     <row r="37" ht="60" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>VRd in LOT1; ALLO on 2025-09-15 (LOT1 ends 2025-09-14). Next MM therapy DARA on 2025-12-10 starts LOT3.</t>
+          <t>VRd in LOT1; ALLO on 2025-09-15 (LOT1 ends 2025-09-14). DARA on 2025-12-10 starts LOT3.</t>
         </is>
       </c>
       <c r="B37" s="10" t="n"/>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>ALLO_DT (always starts a new LOT).</t>
+          <t>ALLO always starts a new LOT.</t>
         </is>
       </c>
       <c r="D40" s="9" t="n"/>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>ALLO LOT contains NO MM therapies.</t>
+          <t>ALLO LOT has no MM drugs.</t>
         </is>
       </c>
       <c r="D42" s="9" t="n"/>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>ALLO LOT spans a single day, so end = ALLO_DT.</t>
+          <t>ALLO LOT = 1 day.</t>
         </is>
       </c>
       <c r="D45" s="9" t="n"/>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>DARA - first MM agent after LOT2.</t>
+          <t>First MM drug after LOT2.</t>
         </is>
       </c>
       <c r="D47" s="9" t="n"/>
@@ -2316,14 +2316,14 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>WORKED EXAMPLE C - LOT3 starts on an AUTO (first-ever; LOT2 ended outside its induction window)</t>
+          <t>WORKED EXAMPLE C - LOT3 starts on a first-ever AUTO</t>
         </is>
       </c>
     </row>
     <row r="51" ht="60" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>LOT1 ends 2025-04-30 via DISCONTINUATION (VRd run-out, no SCT during LOT1). LOT2 starts 2025-08-20 via MED_ADD (DARA + LENA, 30d induction window). First-ever AUTO occurs 2025-12-10, well outside LOT2's 30d induction window (2025-08-20 to 2025-09-18) and not within sct_tandem_days (&lt;=180d) of any prior AUTO. Per Q16 (LOT2-5 only), this first-ever AUTO triggers LOT3 starting on the AUTO date. (LOT1 itself is unchanged - first AUTO in LOT1 would still be protocol-mandated induction.)</t>
+          <t>LOT1 ends 2025-04-30 (DISCONTINUATION). LOT2 is MED-started 2025-08-20 (DARA+LENA). A first-ever AUTO on 2025-12-10 is outside LOT2's 30d window and not a tandem, so it starts LOT3. (LOT2-5 only; in LOT1 the first AUTO would still be induction.)</t>
         </is>
       </c>
       <c r="B51" s="10" t="n"/>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>AUTO outside LOT2's 30d window (LOT2 was MED-started) and not a planned tandem.</t>
+          <t>AUTO outside LOT2's 30d window, not a tandem.</t>
         </is>
       </c>
       <c r="D54" s="9" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>AUTO is a first-class LOT-start trigger for LOT2-5 (Q16). Planned tandem (within sct_tandem_days = 180d of a prior AUTO) would NOT start a new LOT.</t>
+          <t>A first-ever AUTO can start a LOT (LOT2-5 only).</t>
         </is>
       </c>
       <c r="D55" s="9" t="n"/>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>No MM therapies recorded in the [2025-12-10, 2026-01-08] post-AUTO induction window.</t>
+          <t>No MM drugs in the post-AUTO window [2025-12-10, 2026-01-08].</t>
         </is>
       </c>
       <c r="D56" s="9" t="n"/>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>AUTO-only LOT; med count is 0.</t>
+          <t>AUTO-only LOT.</t>
         </is>
       </c>
       <c r="D57" s="9" t="n"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>LOT3 captures any post-AUTO agents within [2025-12-10, 2026-01-08].</t>
+          <t>Post-AUTO window [2025-12-10, 2026-01-08].</t>
         </is>
       </c>
       <c r="D58" s="9" t="n"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>AUTO occurred during LOT3.</t>
+          <t>AUTO during LOT3.</t>
         </is>
       </c>
       <c r="D59" s="9" t="n"/>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Single AUTO during LOT3 (no second AUTO within tandem window).</t>
+          <t>Single AUTO (no tandem).</t>
         </is>
       </c>
       <c r="D60" s="9" t="n"/>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>PRIMARY: earliest of (1) all-agent discontinuation (run-out date); (2) new qualifying MM agent (day before MAP_START_DT); (3) ALLO SCT (day before); (4) AUTO that triggers a new LOT (day before), per the LOTN_START_DT trigger rule (any AUTO outside LOT N's applicable window and not within sct_tandem_days (&lt;=180d) of a prior AUTO); (5) CAR-T (day before FIRST_CART_DT); (6) CART_INIT: when CAR-T occurs within 45 days of the first new agent that breaks LOT N, the new agent is consolidated into CART_INIT and the LOT ends at FIRST_CART_DT - 1; (7) death (YMDOD); (8) study_end. Disenrollment is NOT a primary end event. SENSITIVITY: additionally cap at ENDDATE_CE when CENSOR_AT_DISENROLLMENT = TRUE.</t>
+          <t>PRIMARY: the earliest of (1) run-out (all drugs gone); (2) a new MM drug (day before its start); (3) ALLO SCT (day before); (4) an AUTO that starts a new LOT (day before); (5) CAR-T (day before FIRST_CART_DT); (6) CART_INIT - CAR-T within 45 days of the first drug that breaks LOT N (LOT ends FIRST_CART_DT - 1); (7) death; (8) study end. Disenrollment is not a primary end. SENSITIVITY: also cap at ENDDATE_CE when CENSOR_AT_DISENROLLMENT = TRUE.</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>Primary path inherits LOT1 logic; only induction window differs.</t>
+          <t>Same as LOT1 except the induction window.</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>max(MAP_END_DT) across LOT N induction agents - i.e., the last day of supply for any drug in the regimen. Populated whenever a runout exists, INCLUDING when a higher-priority reason (DEATH, SCT, etc.) wins the LOT end. Used as LOTN_BASE_END_DT only when LOTN_BASE_END_REASON = DISCONTINUATION.</t>
+          <t>Last day of supply across LOT N drugs (max MAP_END_DT). Always set when a run-out exists, even if a higher-priority reason (death, SCT) ends the LOT. Used as the end date only when reason = DISCONTINUATION.</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>T_MEDICAL: FST_DT + medical_day_supply - 1. T_RX: FILL_DT + DAYS_SUP - 1. Missing DAY_SUPPLY -&gt; 28d default (do not delete claims). There is only ONE 90-day rule in the pipeline: the MAP-level per-drug rule (map_discon_gap_days). It says a drug is discontinued if there is no refill within 90 days. There is no additional LOT-level wait on top of that.</t>
+          <t>T_MEDICAL: FST_DT + medical_day_supply - 1. T_RX: FILL_DT + DAYS_SUP - 1. Missing DAY_SUPPLY -&gt; 28d (keep claims). Only one 90-day rule exists: the per-drug MAP rule (no refill in 90d = discontinued). No extra LOT-level wait.</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>First non-steroid MM agent after the induction window with MAP_START_DT &lt;= LOTN_BASE_DISCON_DT, not in LOTN_BASE_MEDS or its biosimilar.</t>
+          <t>First non-steroid MM drug after the induction window, on/before run-out, not in LOTN_BASE_MEDS or a biosimilar of it.</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Audit / debug output column (emitted to LOT_LONG), not a primary analysis variable. Check permissible_subs before classifying as a new add.</t>
+          <t>Audit/debug output (in LOT_LONG), not a primary variable. Check permissible_subs first.</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr"/>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Any ALLO ends current LOT day before ALLO, and starts a new ALLO LOT.</t>
+          <t>Any ALLO ends the current LOT the day before, and starts a new ALLO LOT.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>AUTO claims are first grouped into discrete transplant events in tx_auto_dates. Two AUTO claims/events LESS THAN 60 days apart are treated as the SAME AUTO event - the near-duplicate is not a separate AUTO event, so it forms no tandem pairing and is not a separate trigger (the retained single AUTO event is still evaluated by the normal trigger rule). Among distinct AUTO events: a second AUTO 60-180 days after the first is a planned tandem (continuation, same LOT, no new trigger); an AUTO more than 180 days after the prior AUTO is unplanned and starts a new LOT if it also falls outside LOT N's applicable window.</t>
+          <t>AUTOs are grouped into events first. Two AUTOs &lt;60 days apart = ONE event (the close one is not a separate event, so no tandem and no separate trigger). Two distinct AUTOs 60-180 days apart = planned tandem (same LOT). An AUTO &gt;180 days after the prior one starts a new LOT if it is also outside LOT N's window.</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Per Julia 13-May: the &lt; 60 d merge is handled upstream in tx_auto_dates (sct_auto_gap_days = 60), so tandem classification only needs the &lt;= 180 d (sct_tandem_days) upper bound. Matches LOT1's existing behaviour. Use datediff without +1.</t>
+          <t>The &lt;60d merge happens upstream (tx_auto_dates, sct_auto_gap_days=60), so tandem only needs the &lt;=180d bound. datediff, no +1.</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr"/>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Agents within 45 days of FIRST_CART_DT are consolidated into the CAR-T LOT (study-team decision).</t>
+          <t>Drugs within 45 days of FIRST_CART_DT belong to the CAR-T LOT.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Do NOT advance to LOT_(N+1) for consolidated agents.</t>
+          <t>Consolidated drugs do not start LOT_(N+1).</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr"/>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Earliest qualifying end event from LOTN_END_DT_TEMP. Also: CART_INIT applies when a CAR-T infusion occurs within 45 days of the first new agent that breaks LOT N.</t>
+          <t>Earliest qualifying end from LOTN_END_DT_TEMP. CART_INIT applies if CAR-T is within 45 days of the first drug that breaks LOT N.</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>ALLO LOT spans a single day, start = end = ALLO_DT. CAR-T LOT spans through last consolidation MAP_END_DT. Under CART_INIT the pre-CAR-T bridge agent only marks the CART_INIT transition (LOT N ends at FIRST_CART_DT - 1); it does NOT create a separate non-CAR-T LOT and is NOT carried into the CAR-T LOT regimen (CAR-T induction meds use MAP_START_DT &gt;= FIRST_CART_DT).</t>
+          <t>ALLO LOT = 1 day (start = end = ALLO_DT). CAR-T LOT runs to the last consolidation drug's end. Under CART_INIT the pre-CAR-T bridge drug only marks the switch (LOT N ends FIRST_CART_DT - 1); it does not make its own LOT and is not in the CAR-T regimen (CAR-T meds start on/after FIRST_CART_DT).</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Reason corresponding to LOTN_BASE_END_DT. DISENROLLMENT only in sensitivity (see *_CE_SENS).</t>
+          <t>Reason for LOTN_BASE_END_DT. DISENROLLMENT only in sensitivity (see *_CE_SENS).</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Same-day / overlapping-event priority (revised per Julia 06-May to keep DEATH above DISCONTINUATION): SCT_ALLO &gt; SCT_CART &gt; SCT_AUTO &gt; CART_INIT &gt; MED_ADD &gt; DEATH &gt; DISCONTINUATION &gt; STUDY_END. DEATH outranks DISCONTINUATION so patients who run out then die keep REASON = DEATH (the runout date is still recorded in LOTN_BASE_DISCON_DT). EXCEPTION (Q1.1): if a patient runs out and then starts a new LOT trigger (new MM agent, ALLO, CART, or qualifying AUTO) before death, DISCONTINUATION wins at the runout date and the new trigger starts LOT N+1 - DEATH does not silently swallow post-runout therapy.</t>
+          <t>Priority when events overlap: SCT_ALLO &gt; SCT_CART &gt; SCT_AUTO &gt; CART_INIT &gt; MED_ADD &gt; DEATH &gt; DISCONTINUATION &gt; STUDY_END. DEATH beats DISCONTINUATION, so run-out-then-death keeps DEATH (run-out date still in LOTN_BASE_DISCON_DT). Exception: if a new LOT trigger (new drug, ALLO, CART, qualifying AUTO) happens after run-out but before death, DISCONTINUATION wins at the run-out date and the trigger starts LOT N+1.</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr"/>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Same as LOTN_BASE_END_DT, additionally capped at ELIGEND. Emitted when CENSOR_AT_DISENROLLMENT = TRUE.</t>
+          <t>Same as LOTN_BASE_END_DT but capped at ELIGEND. Emitted when CENSOR_AT_DISENROLLMENT = TRUE.</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Primary LOTN_BASE_END_DT untouched.</t>
+          <t>Primary end date unchanged.</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>REQUIRED: emit DISENROLLMENT (do NOT collapse to STUDY_END). Diverges from current LOT1 behaviour.</t>
+          <t>Emit DISENROLLMENT (do not collapse to STUDY_END). Differs from LOT1.</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr"/>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>If reason = DISCONTINUATION: LOTN_BASE_DISCON_DT - LOTN_START_DT + 1. Else: LOTN_BASE_END_DT - LOTN_START_DT + 1.</t>
+          <t>DISCONTINUATION: DISCON_DT - START_DT + 1. Else: END_DT - START_DT + 1.</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>max(MAP_END_DT) across LOT2 induction agents (last med date).</t>
+          <t>Last med date (max MAP_END_DT) across LOT2 drugs.</t>
         </is>
       </c>
       <c r="D27" s="9" t="n"/>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Runout = LOT end. The only 90-day rule is the per-drug MAP-level one; there is no separate LOT-level wait.</t>
+          <t>Run-out = LOT end. Only the per-drug 90d rule applies; no LOT-level wait.</t>
         </is>
       </c>
       <c r="D28" s="9" t="n"/>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Runout reached; no death or higher-priority event.</t>
+          <t>Run-out reached; nothing higher-priority.</t>
         </is>
       </c>
       <c r="D29" s="9" t="n"/>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>No MM therapies in this LOT.</t>
+          <t>No MM drugs in this LOT.</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>ALLO LOT spans a single day: start = end = ALLO_DT.</t>
+          <t>ALLO LOT = 1 day: start = end = ALLO_DT.</t>
         </is>
       </c>
     </row>
@@ -3628,17 +3628,17 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Agents within 45 days of FIRST_CART_DT are consolidated into this LOT.</t>
+          <t>Drugs within 45 days of FIRST_CART_DT belong to this LOT.</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>SCT_CART (or CART_INIT if CAR-T within 45 days of the first new agent that breaks LOT_(N-1))</t>
+          <t>SCT_CART (or CART_INIT if CAR-T within 45 days of the first drug that breaks LOT_(N-1))</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>45-day consolidation window (study-team decision). When CART_INIT applies, the pre-CAR-T bridge agent only identifies the transition into the CAR-T LOT; it does NOT create a separate non-CAR-T LOT (do not advance to LOT_(N+1) for consolidated agents).</t>
+          <t>45-day window. Under CART_INIT the pre-CAR-T bridge drug only marks the switch; it does not make its own LOT (consolidated drugs do not start LOT_(N+1)).</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Always, UNLESS (i) within LOT_(N-1)'s applicable window (30d MED/AUTO, 1d ALLO, 45d CART) or (ii) within sct_tandem_days (&lt;=180d) of a prior AUTO (planned tandem).</t>
+          <t>Always, unless (i) inside LOT_(N-1)'s window (30d MED/AUTO, 1d ALLO, 45d CART) or (ii) &lt;=180d after a prior AUTO (planned tandem).</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>First-ever AUTOs CAN trigger a new LOT (LOT2-5 only). LOT1 keeps protocol convention that the first AUTO is part of induction. AUTO claims &lt; 60 days apart are merged into a single AUTO event upstream (tx_auto_dates, sct_auto_gap_days = 60) and never count as a separate trigger or as a tandem.</t>
+          <t>A first-ever AUTO can start a LOT (LOT2-5 only; in LOT1 the first AUTO is induction). AUTOs &lt;60 days apart are merged into one event upstream and never count as a separate trigger or tandem.</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Always, when the agent appears strictly after LOT_(N-1)_BASE_END_DT (the prior LOT has ended; for medication-driven transitions the agent must also fall outside the prior LOT's induction/consolidation window) and no higher-priority SCT/CAR-T event shares that start date.</t>
+          <t>Any qualifying MM drug starting after LOT_(N-1) ends (MAP_START_DT &gt; LOT_(N-1)_BASE_END_DT), unless a higher-priority SCT/CAR-T shares that date.</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Starts a new LOT when a non-steroid, non-biosimilar MM agent appears after LOT_(N-1)_BASE_END_DT, regardless of the prior LOT's end reason. Same-day start priority still applies: SCT_ALLO &gt; CART &gt; SCT_AUTO &gt; MED.</t>
+          <t>Any non-steroid, non-biosimilar MM drug after LOT_(N-1) ends starts a LOT, whatever the prior LOT's end reason. Same-day priority: SCT_ALLO &gt; CART &gt; SCT_AUTO &gt; MED.</t>
         </is>
       </c>
     </row>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Death and study end do not start a new LOT. If the patient runs out of regimen therapy, the LOT ends as DISCONTINUATION. If the patient starts a new MM therapy after runout, that therapy starts the next LOT. Death only becomes the end reason when no next-LOT trigger occurs first. Disenrollment is NOT a primary end event.</t>
+          <t>Death and study end never start a LOT. Run-out -&gt; DISCONTINUATION. A new drug after run-out starts the next LOT. Death is the end reason only if no next-LOT trigger comes first. Disenrollment is not a primary end.</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>LOT1 ends d199. LOT2_START_DT=d200, TYPE=MED. Induction d200-d229.</t>
+          <t>LOT1 ends d199. LOT2 starts d200, TYPE=MED. Induction d200-d229.</t>
         </is>
       </c>
     </row>
@@ -3831,12 +3831,12 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>LOT2 is MED-started (30d window). AUTO occurs d320 relative to LOT2 start, outside LOT2's window and not within sct_tandem_days (&lt;=180d) of any prior AUTO.</t>
+          <t>LOT2 MED-started (30d window). AUTO at d320 - outside LOT2's window, not within 180d of a prior AUTO.</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>LOT2 ends d319. LOT3_START_DT = d320, TYPE = SCT_AUTO. Q16 applies to LOT2-5 only; LOT1's first AUTO remains part of induction.</t>
+          <t>LOT2 ends d319. LOT3 starts d320, TYPE=SCT_AUTO. LOT2-5 only; LOT1's first AUTO stays induction.</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>LOT2: start = end = ALLO_DT, single-day ALLO LOT, no MM. Next agent starts LOT3.</t>
+          <t>LOT2: start = end = ALLO_DT (1-day ALLO LOT, no MM). Next drug starts LOT3.</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>LOT2_START_DT=FIRST_CART_DT, TYPE=CART. Agents within 45d consolidated.</t>
+          <t>LOT2 starts FIRST_CART_DT, TYPE=CART. Drugs within 45d belong to it.</t>
         </is>
       </c>
     </row>
@@ -3882,12 +3882,12 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Run-out, then new agent 200d later.</t>
+          <t>Run-out, then new drug 200d later.</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>LOT2 ends DISCONTINUATION. LOT3_START_DT = first new agent.</t>
+          <t>LOT2 ends DISCONTINUATION. LOT3 starts on the new drug.</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>LOT3_BASE_END_DT=YMDOD, reason=DEATH. No LOT4.</t>
+          <t>LOT3 ends at death (YMDOD), reason=DEATH. No LOT4.</t>
         </is>
       </c>
     </row>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Two AUTO claims/events 40 days apart during LOT2.</t>
+          <t>Two AUTOs 40 days apart in LOT2.</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Merged into a single AUTO event upstream (tx_auto_dates, sct_auto_gap_days=60). The near-duplicate is not a separate AUTO event: no tandem (AUTO_TAND_FLG=0) and not a separate trigger; the retained single event is still evaluated by the normal AUTO trigger rule.</t>
+          <t>Merged into one AUTO event upstream. No tandem (AUTO_TAND_FLG=0) and not a separate trigger; the single event is still evaluated normally.</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Single-day ALLO LOT: start = end = ALLO_DT.</t>
+          <t>1-day ALLO LOT: start = end = ALLO_DT.</t>
         </is>
       </c>
     </row>
@@ -4001,12 +4001,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>CAR-T within 45 days of the first new drug add that breaks LOT1.</t>
+          <t>CAR-T within 45 days of the first new drug that breaks LOT1.</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>LOT1 ends with CART_INIT (LOT1 spec). LOT2_START_TYPE = CART.</t>
+          <t>LOT1 ends with CART_INIT. LOT2 TYPE=CART.</t>
         </is>
       </c>
     </row>

--- a/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
+++ b/May 12 2026/Program Specs/lot2to5_spec_DRAFT_may13.xlsx
@@ -3697,12 +3697,12 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>MED_ADD or DISCONTINUATION - set by LOT_(N-1)'s own end logic; this trigger does not override it.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Any non-steroid, non-biosimilar MM drug after LOT_(N-1) ends starts a LOT, whatever the prior LOT's end reason. Same-day priority: SCT_ALLO &gt; CART &gt; SCT_AUTO &gt; MED.</t>
+          <t>Any non-steroid, non-biosimilar MM drug after LOT_(N-1) ends starts a LOT. Same-day priority: SCT_ALLO &gt; CART &gt; SCT_AUTO &gt; MED.</t>
         </is>
       </c>
     </row>
